--- a/04_models/lcr-tt50-2026.xlsx
+++ b/04_models/lcr-tt50-2026.xlsx
@@ -21,13 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -122,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -177,11 +176,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -221,32 +231,32 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -255,20 +265,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -277,26 +287,66 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1029,7 +1079,7 @@
           <t>Ngày chốt số liệu</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="55" t="n">
         <v>47208</v>
       </c>
       <c r="D6" s="16" t="n"/>
@@ -1095,7 +1145,7 @@
           <t>Ngày đầu tháng sau tháng đăng ký (nếu Đ13.2.a)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n"/>
+      <c r="C10" s="55" t="n"/>
       <c r="D10" s="16" t="n"/>
     </row>
     <row r="11">
@@ -1105,7 +1155,7 @@
           <t>Ngày bắt đầu lộ trình</t>
         </is>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="56">
         <f>IF(C9="Đ13.1",ThamSo!$E$82,C10)</f>
         <v/>
       </c>
@@ -1118,7 +1168,7 @@
           <t>Ngưỡng ghi đè (tuỳ chọn)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n"/>
+      <c r="C12" s="57" t="n"/>
       <c r="D12" s="18" t="inlineStr">
         <is>
           <t>Để trống để dùng lộ trình. Nhập khi tính LCR VNĐ/ngoại tệ/hợp nhất theo ngưỡng nội bộ, hoặc khi áp ngưỡng 100% theo Đ13.2.b/Đ13.3.</t>
@@ -1166,11 +1216,11 @@
           <t>Năm thứ 1</t>
         </is>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="58">
         <f>DATE(YEAR($C$11)+0,MONTH($C$11),DAY($C$11))</f>
         <v/>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="59">
         <f>ThamSo!$E$75</f>
         <v/>
       </c>
@@ -1182,11 +1232,11 @@
           <t>Năm thứ 2</t>
         </is>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="58">
         <f>DATE(YEAR($C$11)+1,MONTH($C$11),DAY($C$11))</f>
         <v/>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="59">
         <f>ThamSo!$E$76</f>
         <v/>
       </c>
@@ -1198,11 +1248,11 @@
           <t>Năm thứ 3</t>
         </is>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="58">
         <f>DATE(YEAR($C$11)+2,MONTH($C$11),DAY($C$11))</f>
         <v/>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="59">
         <f>ThamSo!$E$77</f>
         <v/>
       </c>
@@ -1214,11 +1264,11 @@
           <t>Năm thứ 4</t>
         </is>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="58">
         <f>DATE(YEAR($C$11)+3,MONTH($C$11),DAY($C$11))</f>
         <v/>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="59">
         <f>ThamSo!$E$78</f>
         <v/>
       </c>
@@ -1230,11 +1280,11 @@
           <t>Năm thứ 5</t>
         </is>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="58">
         <f>DATE(YEAR($C$11)+4,MONTH($C$11),DAY($C$11))</f>
         <v/>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="59">
         <f>ThamSo!$E$79</f>
         <v/>
       </c>
@@ -1246,11 +1296,11 @@
           <t>Năm thứ 6 trở đi</t>
         </is>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="58">
         <f>DATE(YEAR($C$11)+5,MONTH($C$11),DAY($C$11))</f>
         <v/>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="59">
         <f>ThamSo!$E$80</f>
         <v/>
       </c>
@@ -1278,7 +1328,7 @@
           <t>Giá trị HQLA đủ điều kiện</t>
         </is>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="60">
         <f>HQLA!G34</f>
         <v/>
       </c>
@@ -1295,7 +1345,7 @@
           <t>Tổng dòng tiền ra</t>
         </is>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="60">
         <f>DongTienRa!I57</f>
         <v/>
       </c>
@@ -1312,7 +1362,7 @@
           <t>Tổng dòng tiền vào (trước trần)</t>
         </is>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="60">
         <f>DongTienVao!I30</f>
         <v/>
       </c>
@@ -1329,7 +1379,7 @@
           <t>Trần dòng tiền vào = 75% × Tổng dòng tiền ra</t>
         </is>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="60">
         <f>ThamSo!$E$73*C25</f>
         <v/>
       </c>
@@ -1346,7 +1396,7 @@
           <t>Dòng tiền vào được tính = Min(dòng vào, trần)</t>
         </is>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="60">
         <f>MIN(C26,C27)</f>
         <v/>
       </c>
@@ -1359,7 +1409,7 @@
           <t>Tổng dòng tiền ra ròng 30 ngày</t>
         </is>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="60">
         <f>C25-C28</f>
         <v/>
       </c>
@@ -1376,7 +1426,7 @@
           <t>Tỷ lệ LCR</t>
         </is>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="61">
         <f>IF(C29&gt;0,C24/C29,"n/a")</f>
         <v/>
       </c>
@@ -1406,7 +1456,7 @@
           <t>Ngưỡng theo lộ trình</t>
         </is>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="62">
         <f>IF(C6&lt;C11,0,INDEX(D16:D21,MATCH(C6,C16:C21,1)))</f>
         <v/>
       </c>
@@ -1419,7 +1469,7 @@
           <t>Ngưỡng áp dụng</t>
         </is>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="62">
         <f>IF(C12="",C32,C12)</f>
         <v/>
       </c>
@@ -1445,7 +1495,7 @@
           <t>HQLA đủ điều kiện phải đáp ứng = Ngưỡng × Dòng tiền ra ròng</t>
         </is>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="60">
         <f>C33*C29</f>
         <v/>
       </c>
@@ -1458,7 +1508,7 @@
           <t>HQLA đủ điều kiện / HQLA phải đáp ứng</t>
         </is>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="62">
         <f>IF(C35&gt;0,C24/C35,"n/a")</f>
         <v/>
       </c>
@@ -1504,7 +1554,7 @@
           <t>Level 1 (sau hệ số)</t>
         </is>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="60">
         <f>HQLA!F6</f>
         <v/>
       </c>
@@ -1517,7 +1567,7 @@
           <t>Level 2A (sau hệ số)</t>
         </is>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="60">
         <f>HQLA!F17</f>
         <v/>
       </c>
@@ -1530,7 +1580,7 @@
           <t>Level 2B (sau hệ số)</t>
         </is>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="60">
         <f>HQLA!F21</f>
         <v/>
       </c>
@@ -1543,7 +1593,7 @@
           <t>KĐC15% + KĐC40% (phần bị loại do trần)</t>
         </is>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="60">
         <f>HQLA!G27+HQLA!G28</f>
         <v/>
       </c>
@@ -1556,7 +1606,7 @@
           <t>Tỷ trọng cấp 2 trong HQLA đủ điều kiện</t>
         </is>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="62">
         <f>IF(C24&gt;0,(C41+C42-C43)/C24,"n/a")</f>
         <v/>
       </c>
@@ -1625,15 +1675,6 @@
           <t>Mỗi hệ số một ô, các sheet tính toán tham chiếu tới đây. Cột 'Dòng raw' là số dòng trong 01_sources/alm/TT50_2026_SBV/TT50_2026_SBV.md. Cột 'Đối chiếu (user)': ghi Y sau khi tự kiểm với văn bản gốc.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n"/>
@@ -1720,7 +1761,7 @@
           <t>Hệ số thanh khoản tài sản cấp 1</t>
         </is>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -1733,7 +1774,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-a2]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-a2]] [[src-tt50-2026-nhnn#^pl1-a2-3c]]</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
@@ -1764,7 +1805,7 @@
           <t>Hệ số thanh khoản tài sản cấp 2A</t>
         </is>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="63" t="n">
         <v>0.85</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1777,7 +1818,7 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-a3]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-a3]] [[src-tt50-2026-nhnn#^pl1-a3-3a]] [[src-tt50-2026-nhnn#^pl1-a3-3b]]</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr"/>
@@ -1804,7 +1845,7 @@
           <t>Hệ số thanh khoản RMBS đủ điều kiện (cấp 2B)</t>
         </is>
       </c>
-      <c r="E7" s="31" t="n">
+      <c r="E7" s="63" t="n">
         <v>0.75</v>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -1817,7 +1858,7 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-a4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-a4]] [[src-tt50-2026-nhnn#^pl1-a4-3a]]</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr"/>
@@ -1844,7 +1885,7 @@
           <t>Hệ số thanh khoản chứng khoán nợ DN từ BBB- (cấp 2B)</t>
         </is>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1857,7 +1898,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-a4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-a4]] [[src-tt50-2026-nhnn#^pl1-a4-3b]]</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr"/>
@@ -1884,7 +1925,7 @@
           <t>Hệ số thanh khoản chứng khoán Chính phủ/NHTW nước ngoài từ BBB- (cấp 2B)</t>
         </is>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -1897,7 +1938,7 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-a4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-a4]] [[src-tt50-2026-nhnn#^pl1-a4-3b]]</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr"/>
@@ -1924,7 +1965,7 @@
           <t>Hệ số thanh khoản cổ phiếu phổ thông đủ điều kiện (cấp 2B)</t>
         </is>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E10" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1937,7 +1978,7 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-a4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-a4]] [[src-tt50-2026-nhnn#^pl1-a4-3d]]</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr"/>
@@ -1964,7 +2005,7 @@
           <t>Hệ số thanh khoản tài sản cấp 2B của chi nhánh ở nước ngoài</t>
         </is>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="64" t="n">
         <v>0.5</v>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -1977,7 +2018,7 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-a4-3d]]</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -2008,7 +2049,7 @@
           <t>Hệ số 15/85 trong KĐC15%</t>
         </is>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E12" s="65" t="n">
         <v>0.1764705882352941</v>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -2052,7 +2093,7 @@
           <t>Hệ số 15/60 trong KĐC15%</t>
         </is>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E13" s="65" t="n">
         <v>0.25</v>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -2092,7 +2133,7 @@
           <t>Hệ số 2/3 trong KĐC40%</t>
         </is>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="65" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -2136,7 +2177,7 @@
           <t>Trần hạn mức ngân hàng mẹ (tổng) / HQLA phải đáp ứng</t>
         </is>
       </c>
-      <c r="E15" s="31" t="n">
+      <c r="E15" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -2149,7 +2190,7 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-a1-4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-a1-4]] [[src-tt50-2026-nhnn#^pl1-a1-5]]</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -2180,7 +2221,7 @@
           <t>Trần hạn mức không đối ứng HQLA cấp 1 / HQLA phải đáp ứng</t>
         </is>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="63" t="n">
         <v>0.4</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -2193,7 +2234,7 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-a1-4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-a1-4]] [[src-tt50-2026-nhnn#^pl1-a1-5]]</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
@@ -2224,7 +2265,7 @@
           <t>Tiền gửi bán lẻ ổn định</t>
         </is>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="63" t="n">
         <v>0.05</v>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -2264,7 +2305,7 @@
           <t>Tiền gửi bán lẻ kém ổn định</t>
         </is>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2308,7 +2349,7 @@
           <t>Tiền gửi DNNVV đủ điều kiện — ổn định</t>
         </is>
       </c>
-      <c r="E19" s="31" t="n">
+      <c r="E19" s="63" t="n">
         <v>0.05</v>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -2352,7 +2393,7 @@
           <t>Tiền gửi DNNVV đủ điều kiện — kém ổn định</t>
         </is>
       </c>
-      <c r="E20" s="31" t="n">
+      <c r="E20" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2396,7 +2437,7 @@
           <t>Tiền gửi hoạt động</t>
         </is>
       </c>
-      <c r="E21" s="31" t="n">
+      <c r="E21" s="63" t="n">
         <v>0.25</v>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -2440,7 +2481,7 @@
           <t>Nguồn vốn từ DN, Chính phủ, NHTW, PSE, tổ chức tài chính quốc tế</t>
         </is>
       </c>
-      <c r="E22" s="31" t="n">
+      <c r="E22" s="63" t="n">
         <v>0.4</v>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2480,7 +2521,7 @@
           <t>Nguồn vốn không có bảo đảm khác</t>
         </is>
       </c>
-      <c r="E23" s="31" t="n">
+      <c r="E23" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -2520,7 +2561,7 @@
           <t>Có bảo đảm bằng HQLA cấp 1 / giao dịch với NHNN</t>
         </is>
       </c>
-      <c r="E24" s="31" t="n">
+      <c r="E24" s="63" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2560,7 +2601,7 @@
           <t>Có bảo đảm bằng HQLA cấp 2A</t>
         </is>
       </c>
-      <c r="E25" s="31" t="n">
+      <c r="E25" s="63" t="n">
         <v>0.15</v>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -2600,7 +2641,7 @@
           <t>Có bảo đảm bằng tài sản khác, đối tác Chính phủ/KBNN/UBND/NHCS/VAMC/DATC/BHTG/BHXH/TCTC quốc tế</t>
         </is>
       </c>
-      <c r="E26" s="31" t="n">
+      <c r="E26" s="63" t="n">
         <v>0.25</v>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2640,7 +2681,7 @@
           <t>Có bảo đảm bằng RMBS cấp 2B</t>
         </is>
       </c>
-      <c r="E27" s="31" t="n">
+      <c r="E27" s="63" t="n">
         <v>0.25</v>
       </c>
       <c r="F27" s="14" t="inlineStr">
@@ -2680,7 +2721,7 @@
           <t>Có bảo đảm bằng HQLA cấp 2B khác</t>
         </is>
       </c>
-      <c r="E28" s="31" t="n">
+      <c r="E28" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2720,7 +2761,7 @@
           <t>Có bảo đảm bằng tài sản tài chính khác</t>
         </is>
       </c>
-      <c r="E29" s="31" t="n">
+      <c r="E29" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -2760,7 +2801,7 @@
           <t>Khả năng thay đổi giá trị tài sản bảo đảm (không phải HQLA cấp 1)</t>
         </is>
       </c>
-      <c r="E30" s="31" t="n">
+      <c r="E30" s="63" t="n">
         <v>0.2</v>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2804,7 +2845,7 @@
           <t>Hạ bậc tín nhiệm tối đa 3 bậc</t>
         </is>
       </c>
-      <c r="E31" s="31" t="n">
+      <c r="E31" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="14" t="inlineStr">
@@ -2844,7 +2885,7 @@
           <t>TSBĐ dư thừa không tách biệt, đối tác có quyền thu hồi</t>
         </is>
       </c>
-      <c r="E32" s="31" t="n">
+      <c r="E32" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -2857,7 +2898,7 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-b4]]</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr"/>
@@ -2884,7 +2925,7 @@
           <t>TSBĐ phải ký quỹ nhưng đối tác chưa yêu cầu</t>
         </is>
       </c>
-      <c r="E33" s="31" t="n">
+      <c r="E33" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
@@ -2897,7 +2938,7 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-b4]]</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr"/>
@@ -2924,7 +2965,7 @@
           <t>Thay đổi định giá thị trường (dòng ký quỹ ròng lớn nhất 30 ngày trong 24 tháng)</t>
         </is>
       </c>
-      <c r="E34" s="31" t="n">
+      <c r="E34" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -2964,7 +3005,7 @@
           <t>Hạn mức chưa sử dụng — cá nhân, DNNVV (tín dụng và thanh khoản)</t>
         </is>
       </c>
-      <c r="E35" s="31" t="n">
+      <c r="E35" s="63" t="n">
         <v>0.05</v>
       </c>
       <c r="F35" s="14" t="inlineStr">
@@ -3004,7 +3045,7 @@
           <t>Hạn mức tín dụng — DN không phải TCTC</t>
         </is>
       </c>
-      <c r="E36" s="31" t="n">
+      <c r="E36" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3044,7 +3085,7 @@
           <t>Hạn mức thanh khoản — DN không phải TCTC</t>
         </is>
       </c>
-      <c r="E37" s="31" t="n">
+      <c r="E37" s="63" t="n">
         <v>0.3</v>
       </c>
       <c r="F37" s="14" t="inlineStr">
@@ -3084,7 +3125,7 @@
           <t>Hạn mức tín dụng — Chính phủ, NHTW, PSE, KBNN, UBND, BHTG, TCTC quốc tế</t>
         </is>
       </c>
-      <c r="E38" s="31" t="n">
+      <c r="E38" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3128,7 +3169,7 @@
           <t>Hạn mức thanh khoản — Chính phủ, NHTW, PSE, KBNN, UBND, BHTG, TCTC quốc tế</t>
         </is>
       </c>
-      <c r="E39" s="31" t="n">
+      <c r="E39" s="63" t="n">
         <v>0.3</v>
       </c>
       <c r="F39" s="14" t="inlineStr">
@@ -3172,7 +3213,7 @@
           <t>Hạn mức chưa sử dụng — TCTD, chi nhánh NHNNg</t>
         </is>
       </c>
-      <c r="E40" s="31" t="n">
+      <c r="E40" s="63" t="n">
         <v>0.4</v>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3212,7 +3253,7 @@
           <t>Hạn mức tín dụng — tổ chức tài chính khác</t>
         </is>
       </c>
-      <c r="E41" s="31" t="n">
+      <c r="E41" s="63" t="n">
         <v>0.4</v>
       </c>
       <c r="F41" s="14" t="inlineStr">
@@ -3252,7 +3293,7 @@
           <t>Hạn mức thanh khoản — tổ chức tài chính khác</t>
         </is>
       </c>
-      <c r="E42" s="31" t="n">
+      <c r="E42" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3292,7 +3333,7 @@
           <t>Hạn mức chưa sử dụng — đối tượng khác</t>
         </is>
       </c>
-      <c r="E43" s="31" t="n">
+      <c r="E43" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="14" t="inlineStr">
@@ -3332,7 +3373,7 @@
           <t>Nghĩa vụ giải ngân/thanh toán trong 30 ngày cho tổ chức tài chính (gồm NHNN)</t>
         </is>
       </c>
-      <c r="E44" s="31" t="n">
+      <c r="E44" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3372,7 +3413,7 @@
           <t>Nghĩa vụ giải ngân/thanh toán trong 30 ngày cho cá nhân, tổ chức khác</t>
         </is>
       </c>
-      <c r="E45" s="31" t="n">
+      <c r="E45" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -3385,7 +3426,7 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-b5]]</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -3416,7 +3457,7 @@
           <t>Ngưỡng: % dòng tiền vào 30 ngày từ cùng nhóm khách hàng</t>
         </is>
       </c>
-      <c r="E46" s="33" t="n">
+      <c r="E46" s="64" t="n">
         <v>0.5</v>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -3429,7 +3470,7 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-b5]]</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
@@ -3460,7 +3501,7 @@
           <t>Nghĩa vụ tiềm ẩn: hạn mức huỷ ngang vô điều kiện; cam kết cung cấp cam kết ngoại bảng khác</t>
         </is>
       </c>
-      <c r="E47" s="31" t="n">
+      <c r="E47" s="63" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -3504,7 +3545,7 @@
           <t>Nghĩa vụ tiềm ẩn: công cụ tài trợ thương mại</t>
         </is>
       </c>
-      <c r="E48" s="31" t="n">
+      <c r="E48" s="63" t="n">
         <v>0.03</v>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -3548,7 +3589,7 @@
           <t>Nghĩa vụ tiềm ẩn: bảo lãnh ngân hàng, dự thầu, thực hiện HĐ; autocallable</t>
         </is>
       </c>
-      <c r="E49" s="31" t="n">
+      <c r="E49" s="63" t="n">
         <v>0.05</v>
       </c>
       <c r="F49" s="14" t="inlineStr">
@@ -3592,7 +3633,7 @@
           <t>Nghĩa vụ tiềm ẩn phi hợp đồng</t>
         </is>
       </c>
-      <c r="E50" s="33" t="n">
+      <c r="E50" s="64" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -3636,7 +3677,7 @@
           <t>Cam kết ngoại bảng khác</t>
         </is>
       </c>
-      <c r="E51" s="33" t="n">
+      <c r="E51" s="64" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="14" t="inlineStr">
@@ -3680,7 +3721,7 @@
           <t>Nghĩa vụ tiềm ẩn đã bị kích hoạt, phải thanh toán trong 30 ngày</t>
         </is>
       </c>
-      <c r="E52" s="31" t="n">
+      <c r="E52" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -3693,7 +3734,7 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-b5-3]]</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr"/>
@@ -3720,7 +3761,7 @@
           <t>Dòng tiền ra ròng từ hợp đồng phái sinh</t>
         </is>
       </c>
-      <c r="E53" s="31" t="n">
+      <c r="E53" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="14" t="inlineStr">
@@ -3760,7 +3801,7 @@
           <t>Dòng tiền ra theo thỏa thuận khác</t>
         </is>
       </c>
-      <c r="E54" s="31" t="n">
+      <c r="E54" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -3773,7 +3814,7 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-b6]]</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr"/>
@@ -3800,7 +3841,7 @@
           <t>Cấp tín dụng có bảo đảm/reverse repo — tài sản cấp 1</t>
         </is>
       </c>
-      <c r="E55" s="31" t="n">
+      <c r="E55" s="63" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -3813,7 +3854,7 @@
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr"/>
@@ -3840,7 +3881,7 @@
           <t>Cấp tín dụng có bảo đảm/reverse repo — tài sản cấp 2A</t>
         </is>
       </c>
-      <c r="E56" s="31" t="n">
+      <c r="E56" s="63" t="n">
         <v>0.15</v>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -3853,7 +3894,7 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c2-2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr"/>
@@ -3880,7 +3921,7 @@
           <t>Cấp tín dụng có bảo đảm/reverse repo — RMBS đủ điều kiện</t>
         </is>
       </c>
-      <c r="E57" s="31" t="n">
+      <c r="E57" s="63" t="n">
         <v>0.25</v>
       </c>
       <c r="F57" s="14" t="inlineStr">
@@ -3893,7 +3934,7 @@
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c2-2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr"/>
@@ -3920,7 +3961,7 @@
           <t>Cấp tín dụng có bảo đảm/reverse repo — tài sản cấp 2B khác</t>
         </is>
       </c>
-      <c r="E58" s="31" t="n">
+      <c r="E58" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -3933,7 +3974,7 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c2-2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr"/>
@@ -3960,7 +4001,7 @@
           <t>Khoản cho vay ký quỹ (margin loans)</t>
         </is>
       </c>
-      <c r="E59" s="31" t="n">
+      <c r="E59" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F59" s="14" t="inlineStr">
@@ -3973,7 +4014,7 @@
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr"/>
@@ -4000,7 +4041,7 @@
           <t>Cấp tín dụng có bảo đảm/reverse repo — tài sản tài chính khác</t>
         </is>
       </c>
-      <c r="E60" s="31" t="n">
+      <c r="E60" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -4013,7 +4054,7 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c2-2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr"/>
@@ -4040,7 +4081,7 @@
           <t>Hạn mức tín dụng/thanh khoản do tổ chức khác cấp cho ngân hàng</t>
         </is>
       </c>
-      <c r="E61" s="31" t="n">
+      <c r="E61" s="63" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="14" t="inlineStr">
@@ -4053,7 +4094,7 @@
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c1]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c3]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -4080,7 +4121,7 @@
           <t>Tiền gửi hoạt động tại tổ chức tài chính khác</t>
         </is>
       </c>
-      <c r="E62" s="31" t="n">
+      <c r="E62" s="63" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -4093,7 +4134,7 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-8a]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr"/>
@@ -4120,7 +4161,7 @@
           <t>Phần tiền gửi hoạt động dư thừa đủ điều kiện</t>
         </is>
       </c>
-      <c r="E63" s="31" t="n">
+      <c r="E63" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -4133,7 +4174,7 @@
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-8b]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr"/>
@@ -4160,7 +4201,7 @@
           <t>Tiền gửi từ hoạt động ngân hàng đại lý</t>
         </is>
       </c>
-      <c r="E64" s="31" t="n">
+      <c r="E64" s="63" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -4173,7 +4214,7 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-9]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr"/>
@@ -4200,7 +4241,7 @@
           <t>Phần tiền gửi đại lý dư thừa đủ điều kiện</t>
         </is>
       </c>
-      <c r="E65" s="31" t="n">
+      <c r="E65" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="14" t="inlineStr">
@@ -4213,7 +4254,7 @@
       </c>
       <c r="H65" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-9]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I65" s="14" t="inlineStr"/>
@@ -4240,7 +4281,7 @@
           <t>Phải thu từ khách hàng bán lẻ, DNNVV đủ điều kiện</t>
         </is>
       </c>
-      <c r="E66" s="31" t="n">
+      <c r="E66" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -4253,7 +4294,7 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-5]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr"/>
@@ -4280,7 +4321,7 @@
           <t>Phải thu từ DN không phải tổ chức tài chính</t>
         </is>
       </c>
-      <c r="E67" s="31" t="n">
+      <c r="E67" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F67" s="14" t="inlineStr">
@@ -4293,7 +4334,7 @@
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-6b]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr"/>
@@ -4320,7 +4361,7 @@
           <t>Phải thu từ Chính phủ, KBNN, UBND, BHTG</t>
         </is>
       </c>
-      <c r="E68" s="31" t="n">
+      <c r="E68" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -4333,7 +4374,7 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-6b]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr"/>
@@ -4360,7 +4401,7 @@
           <t>Phải thu từ tổ chức tài chính quốc tế, PSE nước ngoài, tổ chức khác</t>
         </is>
       </c>
-      <c r="E69" s="31" t="n">
+      <c r="E69" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F69" s="14" t="inlineStr">
@@ -4373,7 +4414,7 @@
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-6b]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I69" s="14" t="inlineStr"/>
@@ -4400,7 +4441,7 @@
           <t>Phải thu từ tổ chức tài chính và NHNN</t>
         </is>
       </c>
-      <c r="E70" s="31" t="n">
+      <c r="E70" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -4413,7 +4454,7 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-6a]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr"/>
@@ -4440,7 +4481,7 @@
           <t>Dòng tiền vào ròng từ công cụ phái sinh</t>
         </is>
       </c>
-      <c r="E71" s="31" t="n">
+      <c r="E71" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="14" t="inlineStr">
@@ -4453,7 +4494,7 @@
       </c>
       <c r="H71" s="14" t="inlineStr">
         <is>
-          <t>chưa có claim trong source note</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c5-1]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I71" s="14" t="inlineStr"/>
@@ -4480,7 +4521,7 @@
           <t>Chứng khoán không thuộc HQLA đáo hạn trong 30 ngày</t>
         </is>
       </c>
-      <c r="E72" s="31" t="n">
+      <c r="E72" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -4493,7 +4534,7 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>[[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>[[src-tt50-2026-nhnn#^pl1-c4-7]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr"/>
@@ -4520,7 +4561,7 @@
           <t>Trần dòng tiền vào / tổng dòng tiền ra</t>
         </is>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E73" s="63" t="n">
         <v>0.75</v>
       </c>
       <c r="F73" s="14" t="inlineStr">
@@ -4560,7 +4601,7 @@
           <t>Ngưỡng nguy cơ mất khả năng chi trả: HQLA đủ điều kiện / HQLA phải đáp ứng</t>
         </is>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E74" s="63" t="n">
         <v>0.9</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -4604,7 +4645,7 @@
           <t>Ngưỡng LCR quy VNĐ riêng lẻ — năm thứ nhất</t>
         </is>
       </c>
-      <c r="E75" s="31" t="n">
+      <c r="E75" s="63" t="n">
         <v>0.5</v>
       </c>
       <c r="F75" s="14" t="inlineStr">
@@ -4644,7 +4685,7 @@
           <t>Ngưỡng LCR quy VNĐ riêng lẻ — năm thứ hai</t>
         </is>
       </c>
-      <c r="E76" s="31" t="n">
+      <c r="E76" s="63" t="n">
         <v>0.6</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -4684,7 +4725,7 @@
           <t>Ngưỡng LCR quy VNĐ riêng lẻ — năm thứ ba</t>
         </is>
       </c>
-      <c r="E77" s="31" t="n">
+      <c r="E77" s="63" t="n">
         <v>0.7</v>
       </c>
       <c r="F77" s="14" t="inlineStr">
@@ -4724,7 +4765,7 @@
           <t>Ngưỡng LCR quy VNĐ riêng lẻ — năm thứ tư</t>
         </is>
       </c>
-      <c r="E78" s="31" t="n">
+      <c r="E78" s="63" t="n">
         <v>0.8</v>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -4764,7 +4805,7 @@
           <t>Ngưỡng LCR quy VNĐ riêng lẻ — năm thứ năm</t>
         </is>
       </c>
-      <c r="E79" s="31" t="n">
+      <c r="E79" s="63" t="n">
         <v>0.9</v>
       </c>
       <c r="F79" s="14" t="inlineStr">
@@ -4804,7 +4845,7 @@
           <t>Ngưỡng LCR quy VNĐ riêng lẻ — năm thứ sáu trở đi</t>
         </is>
       </c>
-      <c r="E80" s="31" t="n">
+      <c r="E80" s="63" t="n">
         <v>1</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -4852,7 +4893,7 @@
           <t>Ngày bắt đầu lộ trình với ngân hàng thuộc Đ13.1</t>
         </is>
       </c>
-      <c r="E82" s="36" t="n">
+      <c r="E82" s="66" t="n">
         <v>47027</v>
       </c>
       <c r="F82" s="22" t="inlineStr">
@@ -4920,14 +4961,6 @@
           <t>Đơn vị: tỷ đồng. Ô nền vàng chữ xanh = nhập liệu (SỐ LIỆU MINH HOẠ). Cột (1): số dư đủ điều kiện theo giá thị trường. Cột (2): giá trị sau unwinding giao dịch có bảo đảm/repo/reverse repo đáo hạn trong 30 ngày — để trống nếu không có giao dịch cần đảo ngược, khi đó (5) lấy theo (1) (PL1.A.I.c).</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n"/>
@@ -5029,17 +5062,17 @@
           <t>Tài sản cấp 1 = ∑(1.1÷1.7)</t>
         </is>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="67">
         <f>C7+C8+C9+C10+C13+C14+C15</f>
         <v/>
       </c>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="42" t="n"/>
-      <c r="F6" s="41">
+      <c r="D6" s="67" t="n"/>
+      <c r="E6" s="68" t="n"/>
+      <c r="F6" s="67">
         <f>F7+F8+F9+F10+F13+F14+F15</f>
         <v/>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="67">
         <f>G7+G8+G9+G10+G13+G14+G15</f>
         <v/>
       </c>
@@ -5057,19 +5090,19 @@
           <t>Tiền mặt</t>
         </is>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="69" t="n">
         <v>3200</v>
       </c>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="24">
+      <c r="D7" s="69" t="n"/>
+      <c r="E7" s="59">
         <f>ThamSo!$E$5</f>
         <v/>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="70">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="70">
         <f>IF(D7="",C7,D7)*E7</f>
         <v/>
       </c>
@@ -5095,21 +5128,21 @@
           <t>Tiền gửi (bao gồm cả tiền gửi dự trữ bắt buộc) tại Ngân hàng Nhà nước</t>
         </is>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="69" t="n">
         <v>14500</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="69" t="n">
         <v>11500</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="59">
         <f>ThamSo!$E$5</f>
         <v/>
       </c>
-      <c r="F8" s="45">
+      <c r="F8" s="70">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="45">
+      <c r="G8" s="70">
         <f>IF(D8="",C8,D8)*E8</f>
         <v/>
       </c>
@@ -5135,19 +5168,19 @@
           <t>Chứng khoán của Chính phủ, NHTW các nước khác, tổ chức công lập của Chính phủ và tổ chức tài chính quốc tế đáp ứng điều kiện và chứng khoán được đảm bảo bởi các đối tượng này</t>
         </is>
       </c>
-      <c r="C9" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="24">
+      <c r="C9" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="69" t="n"/>
+      <c r="E9" s="59">
         <f>ThamSo!$E$5</f>
         <v/>
       </c>
-      <c r="F9" s="45">
+      <c r="F9" s="70">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="70">
         <f>IF(D9="",C9,D9)*E9</f>
         <v/>
       </c>
@@ -5173,17 +5206,17 @@
           <t>Công cụ nợ, trái phiếu Chính phủ Việt Nam hoặc Ngân hàng Nhà nước = (1.4.1) + (1.4.2)</t>
         </is>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="67">
         <f>C11+C12</f>
         <v/>
       </c>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="42" t="n"/>
-      <c r="F10" s="41">
+      <c r="D10" s="67" t="n"/>
+      <c r="E10" s="68" t="n"/>
+      <c r="F10" s="67">
         <f>F11+F12</f>
         <v/>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="67">
         <f>G11+G12</f>
         <v/>
       </c>
@@ -5201,19 +5234,19 @@
           <t xml:space="preserve">  Công cụ nợ bằng VNĐ</t>
         </is>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="69" t="n">
         <v>26000</v>
       </c>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="24">
+      <c r="D11" s="69" t="n"/>
+      <c r="E11" s="59">
         <f>ThamSo!$E$5</f>
         <v/>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="70">
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="70">
         <f>IF(D11="",C11,D11)*E11</f>
         <v/>
       </c>
@@ -5239,19 +5272,19 @@
           <t xml:space="preserve">  Công cụ nợ bằng ngoại tệ</t>
         </is>
       </c>
-      <c r="C12" s="44" t="n">
+      <c r="C12" s="69" t="n">
         <v>800</v>
       </c>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="24">
+      <c r="D12" s="69" t="n"/>
+      <c r="E12" s="59">
         <f>ThamSo!$E$5</f>
         <v/>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="70">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="45">
+      <c r="G12" s="70">
         <f>IF(D12="",C12,D12)*E12</f>
         <v/>
       </c>
@@ -5277,19 +5310,19 @@
           <t>Trái phiếu được Chính phủ bảo lãnh thanh toán 100% giá trị gốc, lãi khi đến hạn; trái phiếu chính quyền địa phương</t>
         </is>
       </c>
-      <c r="C13" s="44" t="n">
+      <c r="C13" s="69" t="n">
         <v>1500</v>
       </c>
-      <c r="D13" s="44" t="n"/>
-      <c r="E13" s="24">
+      <c r="D13" s="69" t="n"/>
+      <c r="E13" s="59">
         <f>ThamSo!$E$5</f>
         <v/>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="70">
         <f>C13*E13</f>
         <v/>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="70">
         <f>IF(D13="",C13,D13)*E13</f>
         <v/>
       </c>
@@ -5315,19 +5348,19 @@
           <t>Tài sản trong danh mục HQLA của chi nhánh ở nước ngoài của ngân hàng thương mại</t>
         </is>
       </c>
-      <c r="C14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="44" t="n"/>
-      <c r="E14" s="24">
+      <c r="C14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="69" t="n"/>
+      <c r="E14" s="59">
         <f>ThamSo!$E$5</f>
         <v/>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="70">
         <f>C14*E14</f>
         <v/>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="70">
         <f>IF(D14="",C14,D14)*E14</f>
         <v/>
       </c>
@@ -5353,19 +5386,19 @@
           <t>Công cụ nợ, trái phiếu của Chính phủ và NHTW của quốc gia mà chi nhánh ở nước ngoài của NHTM đặt trụ sở (tối đa bằng dòng tiền ra ròng của chi nhánh đó)</t>
         </is>
       </c>
-      <c r="C15" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="24">
+      <c r="C15" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="69" t="n"/>
+      <c r="E15" s="59">
         <f>ThamSo!$E$5</f>
         <v/>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="70">
         <f>C15*E15</f>
         <v/>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="70">
         <f>IF(D15="",C15,D15)*E15</f>
         <v/>
       </c>
@@ -5391,17 +5424,17 @@
           <t>Tài sản cấp 2</t>
         </is>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="67">
         <f>C17+C21</f>
         <v/>
       </c>
-      <c r="D16" s="41" t="n"/>
-      <c r="E16" s="42" t="n"/>
-      <c r="F16" s="41">
+      <c r="D16" s="67" t="n"/>
+      <c r="E16" s="68" t="n"/>
+      <c r="F16" s="67">
         <f>F17+F21</f>
         <v/>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="67">
         <f>G17+G21</f>
         <v/>
       </c>
@@ -5419,17 +5452,17 @@
           <t>Tài sản cấp 2A = ∑(2.1.1÷2.1.3)</t>
         </is>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="67">
         <f>C18+C19+C20</f>
         <v/>
       </c>
-      <c r="D17" s="41" t="n"/>
-      <c r="E17" s="42" t="n"/>
-      <c r="F17" s="41">
+      <c r="D17" s="67" t="n"/>
+      <c r="E17" s="68" t="n"/>
+      <c r="F17" s="67">
         <f>F18+F19+F20</f>
         <v/>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="67">
         <f>G18+G19+G20</f>
         <v/>
       </c>
@@ -5447,19 +5480,19 @@
           <t xml:space="preserve">  Chứng khoán của Chính phủ, NHTW, tổ chức tài chính quốc tế và tổ chức công lập của Chính phủ đủ điều kiện với hệ số rủi ro tối đa 20%</t>
         </is>
       </c>
-      <c r="C18" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="44" t="n"/>
-      <c r="E18" s="24">
+      <c r="C18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="69" t="n"/>
+      <c r="E18" s="59">
         <f>ThamSo!$E$6</f>
         <v/>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="70">
         <f>C18*E18</f>
         <v/>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="70">
         <f>IF(D18="",C18,D18)*E18</f>
         <v/>
       </c>
@@ -5485,21 +5518,21 @@
           <t xml:space="preserve">  Chứng khoán nợ của doanh nghiệp đủ điều kiện xếp hạng từ AA- trở lên</t>
         </is>
       </c>
-      <c r="C19" s="44" t="n">
+      <c r="C19" s="69" t="n">
         <v>2400</v>
       </c>
-      <c r="D19" s="44" t="n">
+      <c r="D19" s="69" t="n">
         <v>5400</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="59">
         <f>ThamSo!$E$6</f>
         <v/>
       </c>
-      <c r="F19" s="45">
+      <c r="F19" s="70">
         <f>C19*E19</f>
         <v/>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="70">
         <f>IF(D19="",C19,D19)*E19</f>
         <v/>
       </c>
@@ -5525,19 +5558,19 @@
           <t xml:space="preserve">  Tài sản trong danh mục HQLA của chi nhánh ở nước ngoài của NHTM</t>
         </is>
       </c>
-      <c r="C20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="44" t="n"/>
-      <c r="E20" s="24">
+      <c r="C20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="69" t="n"/>
+      <c r="E20" s="59">
         <f>ThamSo!$E$6</f>
         <v/>
       </c>
-      <c r="F20" s="45">
+      <c r="F20" s="70">
         <f>C20*E20</f>
         <v/>
       </c>
-      <c r="G20" s="45">
+      <c r="G20" s="70">
         <f>IF(D20="",C20,D20)*E20</f>
         <v/>
       </c>
@@ -5563,17 +5596,17 @@
           <t>Tài sản cấp 2B = ∑(2.2.1÷2.2.5)</t>
         </is>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="67">
         <f>C22+C23+C24+C25+C26</f>
         <v/>
       </c>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="42" t="n"/>
-      <c r="F21" s="41">
+      <c r="D21" s="67" t="n"/>
+      <c r="E21" s="68" t="n"/>
+      <c r="F21" s="67">
         <f>F22+F23+F24+F25+F26</f>
         <v/>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="67">
         <f>G22+G23+G24+G25+G26</f>
         <v/>
       </c>
@@ -5591,19 +5624,19 @@
           <t xml:space="preserve">  RMBS đủ điều kiện</t>
         </is>
       </c>
-      <c r="C22" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="44" t="n"/>
-      <c r="E22" s="24">
+      <c r="C22" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="69" t="n"/>
+      <c r="E22" s="59">
         <f>ThamSo!$E$7</f>
         <v/>
       </c>
-      <c r="F22" s="45">
+      <c r="F22" s="70">
         <f>C22*E22</f>
         <v/>
       </c>
-      <c r="G22" s="45">
+      <c r="G22" s="70">
         <f>IF(D22="",C22,D22)*E22</f>
         <v/>
       </c>
@@ -5629,19 +5662,19 @@
           <t xml:space="preserve">  Chứng khoán nợ của doanh nghiệp đủ điều kiện xếp hạng từ BBB- trở lên</t>
         </is>
       </c>
-      <c r="C23" s="44" t="n">
+      <c r="C23" s="69" t="n">
         <v>2600</v>
       </c>
-      <c r="D23" s="44" t="n"/>
-      <c r="E23" s="24">
+      <c r="D23" s="69" t="n"/>
+      <c r="E23" s="59">
         <f>ThamSo!$E$8</f>
         <v/>
       </c>
-      <c r="F23" s="45">
+      <c r="F23" s="70">
         <f>C23*E23</f>
         <v/>
       </c>
-      <c r="G23" s="45">
+      <c r="G23" s="70">
         <f>IF(D23="",C23,D23)*E23</f>
         <v/>
       </c>
@@ -5667,19 +5700,19 @@
           <t xml:space="preserve">  Chứng khoán của Chính phủ, NHTW, PSE hoặc tổ chức tài chính quốc tế đủ điều kiện, xếp hạng BBB- trở lên nhưng không thuộc cấp 1 hoặc 2A</t>
         </is>
       </c>
-      <c r="C24" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="44" t="n"/>
-      <c r="E24" s="24">
+      <c r="C24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="69" t="n"/>
+      <c r="E24" s="59">
         <f>ThamSo!$E$9</f>
         <v/>
       </c>
-      <c r="F24" s="45">
+      <c r="F24" s="70">
         <f>C24*E24</f>
         <v/>
       </c>
-      <c r="G24" s="45">
+      <c r="G24" s="70">
         <f>IF(D24="",C24,D24)*E24</f>
         <v/>
       </c>
@@ -5705,19 +5738,19 @@
           <t xml:space="preserve">  Cổ phiếu phổ thông đủ điều kiện</t>
         </is>
       </c>
-      <c r="C25" s="44" t="n">
+      <c r="C25" s="69" t="n">
         <v>900</v>
       </c>
-      <c r="D25" s="44" t="n"/>
-      <c r="E25" s="24">
+      <c r="D25" s="69" t="n"/>
+      <c r="E25" s="59">
         <f>ThamSo!$E$10</f>
         <v/>
       </c>
-      <c r="F25" s="45">
+      <c r="F25" s="70">
         <f>C25*E25</f>
         <v/>
       </c>
-      <c r="G25" s="45">
+      <c r="G25" s="70">
         <f>IF(D25="",C25,D25)*E25</f>
         <v/>
       </c>
@@ -5743,19 +5776,19 @@
           <t xml:space="preserve">  Tài sản trong danh mục HQLA của chi nhánh ở nước ngoài của NHTM (hệ số theo từng loại)</t>
         </is>
       </c>
-      <c r="C26" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="44" t="n"/>
-      <c r="E26" s="46">
+      <c r="C26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="69" t="n"/>
+      <c r="E26" s="71">
         <f>ThamSo!$E$11</f>
         <v/>
       </c>
-      <c r="F26" s="45">
+      <c r="F26" s="70">
         <f>C26*E26</f>
         <v/>
       </c>
-      <c r="G26" s="45">
+      <c r="G26" s="70">
         <f>IF(D26="",C26,D26)*E26</f>
         <v/>
       </c>
@@ -5781,11 +5814,11 @@
           <t>KĐC15%</t>
         </is>
       </c>
-      <c r="C27" s="41" t="n"/>
-      <c r="D27" s="41" t="n"/>
+      <c r="C27" s="67" t="n"/>
+      <c r="D27" s="67" t="n"/>
       <c r="E27" s="39" t="n"/>
-      <c r="F27" s="41" t="n"/>
-      <c r="G27" s="41">
+      <c r="F27" s="67" t="n"/>
+      <c r="G27" s="67">
         <f>MAX(G21-ThamSo!$E$12*(G6+G17),G21-ThamSo!$E$13*G6,0)</f>
         <v/>
       </c>
@@ -5811,11 +5844,11 @@
           <t>KĐC40%</t>
         </is>
       </c>
-      <c r="C28" s="41" t="n"/>
-      <c r="D28" s="41" t="n"/>
+      <c r="C28" s="67" t="n"/>
+      <c r="D28" s="67" t="n"/>
       <c r="E28" s="39" t="n"/>
-      <c r="F28" s="41" t="n"/>
-      <c r="G28" s="41">
+      <c r="F28" s="67" t="n"/>
+      <c r="G28" s="67">
         <f>MAX(G17+G21-G27-ThamSo!$E$14*G6,0)</f>
         <v/>
       </c>
@@ -5841,11 +5874,11 @@
           <t>Hạn mức = (5.1) + (5.2)</t>
         </is>
       </c>
-      <c r="C29" s="41" t="n"/>
-      <c r="D29" s="41" t="n"/>
+      <c r="C29" s="67" t="n"/>
+      <c r="D29" s="67" t="n"/>
       <c r="E29" s="39" t="n"/>
-      <c r="F29" s="41" t="n"/>
-      <c r="G29" s="41">
+      <c r="F29" s="67" t="n"/>
+      <c r="G29" s="67">
         <f>G30+G31</f>
         <v/>
       </c>
@@ -5863,13 +5896,13 @@
           <t>Hạn mức chưa sử dụng được thiết lập trong giao dịch với Ngân hàng Nhà nước (bảo đảm bằng HQLA cấp 1)</t>
         </is>
       </c>
-      <c r="C30" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="45" t="n"/>
+      <c r="C30" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="70" t="n"/>
       <c r="E30" s="22" t="n"/>
-      <c r="F30" s="45" t="n"/>
-      <c r="G30" s="45">
+      <c r="F30" s="70" t="n"/>
+      <c r="G30" s="70">
         <f>C30</f>
         <v/>
       </c>
@@ -5895,11 +5928,11 @@
           <t>Hạn mức chưa sử dụng của ngân hàng mẹ (chỉ chi nhánh NHNNg) = (5.2.1) + (5.2.2), sau trần</t>
         </is>
       </c>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
+      <c r="C31" s="70" t="n"/>
+      <c r="D31" s="70" t="n"/>
       <c r="E31" s="22" t="n"/>
-      <c r="F31" s="45" t="n"/>
-      <c r="G31" s="45">
+      <c r="F31" s="70" t="n"/>
+      <c r="G31" s="70">
         <f>MIN(G32+G33,ThamSo!$E$15*KetQua!$C$29)</f>
         <v/>
       </c>
@@ -5925,13 +5958,13 @@
           <t xml:space="preserve">  Hạn mức cam kết trên cơ sở đối ứng bởi một danh mục HQLA cấp 1</t>
         </is>
       </c>
-      <c r="C32" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="45" t="n"/>
+      <c r="C32" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="70" t="n"/>
       <c r="E32" s="22" t="n"/>
-      <c r="F32" s="45" t="n"/>
-      <c r="G32" s="45">
+      <c r="F32" s="70" t="n"/>
+      <c r="G32" s="70">
         <f>C32</f>
         <v/>
       </c>
@@ -5953,13 +5986,13 @@
           <t xml:space="preserve">  Hạn mức cam kết không hủy ngang không được đối ứng bởi danh mục HQLA cấp 1 (trần 40%)</t>
         </is>
       </c>
-      <c r="C33" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="45" t="n"/>
+      <c r="C33" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="70" t="n"/>
       <c r="E33" s="22" t="n"/>
-      <c r="F33" s="45" t="n"/>
-      <c r="G33" s="45">
+      <c r="F33" s="70" t="n"/>
+      <c r="G33" s="70">
         <f>MIN(C33,ThamSo!$E$16*KetQua!$C$29)</f>
         <v/>
       </c>
@@ -5980,12 +6013,12 @@
           <t>Giá trị HQLA đủ điều kiện = Level 1 + Level 2A + Level 2B + Hạn mức (Mục 5) – KĐC15% (Mục 3) – KĐC40% (Mục 4)</t>
         </is>
       </c>
-      <c r="B34" s="48" t="n"/>
-      <c r="C34" s="48" t="n"/>
-      <c r="D34" s="48" t="n"/>
-      <c r="E34" s="48" t="n"/>
-      <c r="F34" s="48" t="n"/>
-      <c r="G34" s="49">
+      <c r="B34" s="72" t="n"/>
+      <c r="C34" s="72" t="n"/>
+      <c r="D34" s="72" t="n"/>
+      <c r="E34" s="72" t="n"/>
+      <c r="F34" s="73" t="n"/>
+      <c r="G34" s="74">
         <f>F6+F17+F21+G29-G27-G28</f>
         <v/>
       </c>
@@ -6051,16 +6084,6 @@
           <t>Đơn vị: tỷ đồng. Ô nền vàng chữ xanh = nhập liệu. Số đang có là SỐ LIỆU MINH HOẠ, thay bằng số liệu thật. Cột (1)–(4): số dư đủ điều kiện phân theo thời gian đến hạn theo hợp đồng/dự kiến.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n"/>
@@ -6184,28 +6207,28 @@
           <t>Tiền gửi bán lẻ</t>
         </is>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="67">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="67">
         <f>D7+D8</f>
         <v/>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="67">
         <f>E7+E8</f>
         <v/>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="67">
         <f>F7+F8</f>
         <v/>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="67">
         <f>G7+G8</f>
         <v/>
       </c>
-      <c r="H6" s="42" t="n"/>
-      <c r="I6" s="41">
+      <c r="H6" s="68" t="n"/>
+      <c r="I6" s="67">
         <f>I7+I8</f>
         <v/>
       </c>
@@ -6223,27 +6246,27 @@
           <t>Tiền gửi ổn định</t>
         </is>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="69" t="n">
         <v>1200</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="69" t="n">
         <v>2600</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="69" t="n">
         <v>3100</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="69" t="n">
         <v>9100</v>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="70">
         <f>SUM(C7:F7)</f>
         <v/>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="59">
         <f>ThamSo!$E$17</f>
         <v/>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="70">
         <f>G7*H7</f>
         <v/>
       </c>
@@ -6254,7 +6277,7 @@
       </c>
       <c r="K7" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.II.2.2 (raw dòng 1460); [[src-tt50-2026-nhnn#^pl1-b2]]</t>
+          <t>PL1.B.II.2.2 (raw dòng 1460); [[src-tt50-2026-nhnn#^pl1-b2-2]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6269,27 +6292,27 @@
           <t>Tiền gửi kém ổn định</t>
         </is>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="69" t="n">
         <v>2400</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="69" t="n">
         <v>4800</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="69" t="n">
         <v>5600</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="69" t="n">
         <v>15200</v>
       </c>
-      <c r="G8" s="45">
+      <c r="G8" s="70">
         <f>SUM(C8:F8)</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="59">
         <f>ThamSo!$E$18</f>
         <v/>
       </c>
-      <c r="I8" s="45">
+      <c r="I8" s="70">
         <f>G8*H8</f>
         <v/>
       </c>
@@ -6300,7 +6323,7 @@
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.II.3.2 (raw dòng 1466); [[src-tt50-2026-nhnn#^pl1-b2]]</t>
+          <t>PL1.B.II.3.2 (raw dòng 1466); [[src-tt50-2026-nhnn#^pl1-b2-3]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6315,28 +6338,28 @@
           <t>Nguồn vốn bán buôn không có bảo đảm</t>
         </is>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="67">
         <f>C10+C13+C14+C15</f>
         <v/>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="67">
         <f>D10+D13+D14+D15</f>
         <v/>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="67">
         <f>E10+E13+E14+E15</f>
         <v/>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="67">
         <f>F10+F13+F14+F15</f>
         <v/>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="67">
         <f>G10+G13+G14+G15</f>
         <v/>
       </c>
-      <c r="H9" s="42" t="n"/>
-      <c r="I9" s="41">
+      <c r="H9" s="68" t="n"/>
+      <c r="I9" s="67">
         <f>I10+I13+I14+I15</f>
         <v/>
       </c>
@@ -6354,28 +6377,28 @@
           <t>Tiền gửi từ khách hàng doanh nghiệp nhỏ và vừa đủ điều kiện</t>
         </is>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="67">
         <f>C11+C12</f>
         <v/>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="67">
         <f>D11+D12</f>
         <v/>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="67">
         <f>E11+E12</f>
         <v/>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="67">
         <f>F11+F12</f>
         <v/>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="67">
         <f>G11+G12</f>
         <v/>
       </c>
-      <c r="H10" s="42" t="n"/>
-      <c r="I10" s="41">
+      <c r="H10" s="68" t="n"/>
+      <c r="I10" s="67">
         <f>I11+I12</f>
         <v/>
       </c>
@@ -6393,27 +6416,27 @@
           <t>Tiền gửi ổn định</t>
         </is>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="69" t="n">
         <v>150</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="69" t="n">
         <v>300</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="69" t="n">
         <v>350</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="69" t="n">
         <v>900</v>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="70">
         <f>SUM(C11:F11)</f>
         <v/>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="59">
         <f>ThamSo!$E$19</f>
         <v/>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="70">
         <f>G11*H11</f>
         <v/>
       </c>
@@ -6424,7 +6447,7 @@
       </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.2.2.a(iii) (raw dòng 1502); [[src-tt50-2026-nhnn#^pl1-b3]]</t>
+          <t>PL1.B.III.2.2.a(iii) (raw dòng 1502); [[src-tt50-2026-nhnn#^pl1-b3-22]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6439,27 +6462,27 @@
           <t>Tiền gửi kém ổn định</t>
         </is>
       </c>
-      <c r="C12" s="44" t="n">
+      <c r="C12" s="69" t="n">
         <v>300</v>
       </c>
-      <c r="D12" s="44" t="n">
+      <c r="D12" s="69" t="n">
         <v>600</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="69" t="n">
         <v>700</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="69" t="n">
         <v>1800</v>
       </c>
-      <c r="G12" s="45">
+      <c r="G12" s="70">
         <f>SUM(C12:F12)</f>
         <v/>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="59">
         <f>ThamSo!$E$20</f>
         <v/>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="70">
         <f>G12*H12</f>
         <v/>
       </c>
@@ -6470,7 +6493,7 @@
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.2.2.a(iii) (raw dòng 1502); [[src-tt50-2026-nhnn#^pl1-b3]]</t>
+          <t>PL1.B.III.2.2.a(iii) (raw dòng 1502); [[src-tt50-2026-nhnn#^pl1-b3-22]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6485,27 +6508,27 @@
           <t>Tiền gửi hoạt động</t>
         </is>
       </c>
-      <c r="C13" s="44" t="n">
+      <c r="C13" s="69" t="n">
         <v>1500</v>
       </c>
-      <c r="D13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="45">
+      <c r="D13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="70">
         <f>SUM(C13:F13)</f>
         <v/>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="59">
         <f>ThamSo!$E$21</f>
         <v/>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="70">
         <f>G13*H13</f>
         <v/>
       </c>
@@ -6516,7 +6539,7 @@
       </c>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.2.3.a(ii) (raw dòng 1526); [[src-tt50-2026-nhnn#^pl1-b3]]</t>
+          <t>PL1.B.III.2.3.a(ii) (raw dòng 1526); [[src-tt50-2026-nhnn#^pl1-b3-23a]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6531,27 +6554,27 @@
           <t>Nguồn vốn từ doanh nghiệp và Chính phủ, ngân hàng trung ương, tổ chức công lập của Chính phủ và tổ chức tài chính quốc tế</t>
         </is>
       </c>
-      <c r="C14" s="44" t="n">
+      <c r="C14" s="69" t="n">
         <v>5000</v>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="69" t="n">
         <v>6000</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="69" t="n">
         <v>7000</v>
       </c>
-      <c r="F14" s="44" t="n">
+      <c r="F14" s="69" t="n">
         <v>15000</v>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="70">
         <f>SUM(C14:F14)</f>
         <v/>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="59">
         <f>ThamSo!$E$22</f>
         <v/>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="70">
         <f>G14*H14</f>
         <v/>
       </c>
@@ -6562,7 +6585,7 @@
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.2.4.b (raw dòng 1604); [[src-tt50-2026-nhnn#^pl1-b3]]</t>
+          <t>PL1.B.III.2.4.b (raw dòng 1604); [[src-tt50-2026-nhnn#^pl1-b3-24]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6577,27 +6600,27 @@
           <t>Nguồn vốn không có bảo đảm khác</t>
         </is>
       </c>
-      <c r="C15" s="44" t="n">
+      <c r="C15" s="69" t="n">
         <v>6000</v>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="69" t="n">
         <v>7000</v>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="69" t="n">
         <v>5000</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="69" t="n">
         <v>8000</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="70">
         <f>SUM(C15:F15)</f>
         <v/>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="59">
         <f>ThamSo!$E$23</f>
         <v/>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="70">
         <f>G15*H15</f>
         <v/>
       </c>
@@ -6608,7 +6631,7 @@
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.2.5.b (raw dòng 1610); [[src-tt50-2026-nhnn#^pl1-b3]]</t>
+          <t>PL1.B.III.2.5.b (raw dòng 1610); [[src-tt50-2026-nhnn#^pl1-b3-25]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6623,28 +6646,28 @@
           <t>Nguồn vốn bán buôn có bảo đảm</t>
         </is>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="67">
         <f>C17+C18+C19+C20+C21+C22</f>
         <v/>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="67">
         <f>D17+D18+D19+D20+D21+D22</f>
         <v/>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="67">
         <f>E17+E18+E19+E20+E21+E22</f>
         <v/>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="67">
         <f>F17+F18+F19+F20+F21+F22</f>
         <v/>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="67">
         <f>G17+G18+G19+G20+G21+G22</f>
         <v/>
       </c>
-      <c r="H16" s="42" t="n"/>
-      <c r="I16" s="41">
+      <c r="H16" s="68" t="n"/>
+      <c r="I16" s="67">
         <f>I17+I18+I19+I20+I21+I22</f>
         <v/>
       </c>
@@ -6662,27 +6685,27 @@
           <t>Nguồn vốn được đảm bảo bằng HQLA cấp 1 hoặc nguồn vốn được bảo đảm trong giao dịch với Ngân hàng Nhà nước</t>
         </is>
       </c>
-      <c r="C17" s="44" t="n">
+      <c r="C17" s="69" t="n">
         <v>2000</v>
       </c>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="69" t="n">
         <v>1500</v>
       </c>
-      <c r="E17" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="45">
+      <c r="E17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="70">
         <f>SUM(C17:F17)</f>
         <v/>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="59">
         <f>ThamSo!$E$24</f>
         <v/>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="70">
         <f>G17*H17</f>
         <v/>
       </c>
@@ -6693,7 +6716,7 @@
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.3.2.2.a (raw dòng 1636); [[src-tt50-2026-nhnn#^pl1-b3-3]]</t>
+          <t>PL1.B.III.3.2.2.a (raw dòng 1636); [[src-tt50-2026-nhnn#^pl1-b3-3]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6708,27 +6731,27 @@
           <t>Nguồn vốn được đảm bảo bằng HQLA cấp 2A</t>
         </is>
       </c>
-      <c r="C18" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="44" t="n">
+      <c r="C18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="69" t="n">
         <v>500</v>
       </c>
-      <c r="E18" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="45">
+      <c r="E18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="70">
         <f>SUM(C18:F18)</f>
         <v/>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="59">
         <f>ThamSo!$E$25</f>
         <v/>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="70">
         <f>G18*H18</f>
         <v/>
       </c>
@@ -6739,7 +6762,7 @@
       </c>
       <c r="K18" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.3.2.2.b (raw dòng 1637); [[src-tt50-2026-nhnn#^pl1-b3-3]]</t>
+          <t>PL1.B.III.3.2.2.b (raw dòng 1637); [[src-tt50-2026-nhnn#^pl1-b3-3]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6754,27 +6777,27 @@
           <t>Nguồn vốn được đảm bảo bằng tài sản tài chính khác trong giao dịch với Chính phủ, Kho bạc Nhà nước…</t>
         </is>
       </c>
-      <c r="C19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="45">
+      <c r="C19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="70">
         <f>SUM(C19:F19)</f>
         <v/>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="59">
         <f>ThamSo!$E$26</f>
         <v/>
       </c>
-      <c r="I19" s="45">
+      <c r="I19" s="70">
         <f>G19*H19</f>
         <v/>
       </c>
@@ -6785,7 +6808,7 @@
       </c>
       <c r="K19" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.3.2.2.c (raw dòng 1638); [[src-tt50-2026-nhnn#^pl1-b3-3]]</t>
+          <t>PL1.B.III.3.2.2.c (raw dòng 1638); [[src-tt50-2026-nhnn#^pl1-b3-3]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6800,27 +6823,27 @@
           <t>Nguồn vốn được bảo đảm bằng chứng khoán đảm bảo bằng thế chấp nhà ở (RMBS) đủ điều kiện thuộc cấp 2B</t>
         </is>
       </c>
-      <c r="C20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="45">
+      <c r="C20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="70">
         <f>SUM(C20:F20)</f>
         <v/>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="59">
         <f>ThamSo!$E$27</f>
         <v/>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="70">
         <f>G20*H20</f>
         <v/>
       </c>
@@ -6831,7 +6854,7 @@
       </c>
       <c r="K20" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.3.2.2.d (raw dòng 1639); [[src-tt50-2026-nhnn#^pl1-b3-3]]</t>
+          <t>PL1.B.III.3.2.2.d (raw dòng 1639); [[src-tt50-2026-nhnn#^pl1-b3-3]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6846,27 +6869,27 @@
           <t>Nguồn vốn được bảo đảm bằng các HQLA cấp 2B khác</t>
         </is>
       </c>
-      <c r="C21" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="45">
+      <c r="C21" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="70">
         <f>SUM(C21:F21)</f>
         <v/>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="59">
         <f>ThamSo!$E$28</f>
         <v/>
       </c>
-      <c r="I21" s="45">
+      <c r="I21" s="70">
         <f>G21*H21</f>
         <v/>
       </c>
@@ -6877,7 +6900,7 @@
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.3.2.2.đ (raw dòng 1640); [[src-tt50-2026-nhnn#^pl1-b3-3]]</t>
+          <t>PL1.B.III.3.2.2.đ (raw dòng 1640); [[src-tt50-2026-nhnn#^pl1-b3-3]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6892,27 +6915,27 @@
           <t>Nguồn vốn được đảm bảo bằng các tài sản tài chính khác</t>
         </is>
       </c>
-      <c r="C22" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="44" t="n">
+      <c r="C22" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="69" t="n">
         <v>200</v>
       </c>
-      <c r="F22" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="45">
+      <c r="F22" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="70">
         <f>SUM(C22:F22)</f>
         <v/>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="59">
         <f>ThamSo!$E$29</f>
         <v/>
       </c>
-      <c r="I22" s="45">
+      <c r="I22" s="70">
         <f>G22*H22</f>
         <v/>
       </c>
@@ -6923,7 +6946,7 @@
       </c>
       <c r="K22" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.III.3.2.2.e (raw dòng 1641); [[src-tt50-2026-nhnn#^pl1-b3-3]]</t>
+          <t>PL1.B.III.3.2.2.e (raw dòng 1641); [[src-tt50-2026-nhnn#^pl1-b3-3]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -6938,28 +6961,28 @@
           <t>Yêu cầu bổ sung</t>
         </is>
       </c>
-      <c r="C23" s="41">
+      <c r="C23" s="67">
         <f>C24+C25+C26+C27+C28</f>
         <v/>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="67">
         <f>D24+D25+D26+D27+D28</f>
         <v/>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="67">
         <f>E24+E25+E26+E27+E28</f>
         <v/>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="67">
         <f>F24+F25+F26+F27+F28</f>
         <v/>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="67">
         <f>G24+G25+G26+G27+G28</f>
         <v/>
       </c>
-      <c r="H23" s="42" t="n"/>
-      <c r="I23" s="41">
+      <c r="H23" s="68" t="n"/>
+      <c r="I23" s="67">
         <f>I24+I25+I26+I27+I28</f>
         <v/>
       </c>
@@ -6977,27 +7000,27 @@
           <t>Nhu cầu thanh khoản do khả năng thay đổi giá trị tài sản bảo đảm</t>
         </is>
       </c>
-      <c r="C24" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="44" t="n">
+      <c r="C24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="69" t="n">
         <v>400</v>
       </c>
-      <c r="G24" s="45">
+      <c r="G24" s="70">
         <f>SUM(C24:F24)</f>
         <v/>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="59">
         <f>ThamSo!$E$30</f>
         <v/>
       </c>
-      <c r="I24" s="45">
+      <c r="I24" s="70">
         <f>G24*H24</f>
         <v/>
       </c>
@@ -7008,7 +7031,7 @@
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.IV.2.2.b (raw dòng 1685); [[src-tt50-2026-nhnn#^pl1-b4]]</t>
+          <t>PL1.B.IV.2.2.b (raw dòng 1685); [[src-tt50-2026-nhnn#^pl1-b4-22]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7023,27 +7046,27 @@
           <t>Dòng tiền ra bổ sung khi bị hạ bậc xếp hạng tín nhiệm</t>
         </is>
       </c>
-      <c r="C25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="45">
+      <c r="C25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="70">
         <f>SUM(C25:F25)</f>
         <v/>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="59">
         <f>ThamSo!$E$31</f>
         <v/>
       </c>
-      <c r="I25" s="45">
+      <c r="I25" s="70">
         <f>G25*H25</f>
         <v/>
       </c>
@@ -7054,7 +7077,7 @@
       </c>
       <c r="K25" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.IV.2.1.b (raw dòng 1679); [[src-tt50-2026-nhnn#^pl1-b4]]</t>
+          <t>PL1.B.IV.2.1.b (raw dòng 1679); [[src-tt50-2026-nhnn#^pl1-b4-21]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7069,27 +7092,27 @@
           <t>Dòng tiền ra bổ sung do bên đối tác có quyền yêu cầu thu hồi theo thỏa thuận</t>
         </is>
       </c>
-      <c r="C26" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="45">
+      <c r="C26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="70">
         <f>SUM(C26:F26)</f>
         <v/>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="59">
         <f>ThamSo!$E$32</f>
         <v/>
       </c>
-      <c r="I26" s="45">
+      <c r="I26" s="70">
         <f>G26*H26</f>
         <v/>
       </c>
@@ -7100,7 +7123,7 @@
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.IV.2.3.b (raw dòng 1701); chưa có claim trong source note</t>
+          <t>PL1.B.IV.2.3.b (raw dòng 1701); [[src-tt50-2026-nhnn#^pl1-b4-23]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7115,27 +7138,27 @@
           <t>Dòng tiền ra bổ sung do phải ký quỹ theo thỏa thuận nhưng đối tác chưa yêu cầu ký quỹ</t>
         </is>
       </c>
-      <c r="C27" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="45">
+      <c r="C27" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="70">
         <f>SUM(C27:F27)</f>
         <v/>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="59">
         <f>ThamSo!$E$33</f>
         <v/>
       </c>
-      <c r="I27" s="45">
+      <c r="I27" s="70">
         <f>G27*H27</f>
         <v/>
       </c>
@@ -7146,7 +7169,7 @@
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.IV.2.4 (raw dòng 1705); chưa có claim trong source note</t>
+          <t>PL1.B.IV.2.4 (raw dòng 1705); [[src-tt50-2026-nhnn#^pl1-b4-23]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7161,27 +7184,27 @@
           <t>Dòng tiền ra bổ sung do thay đổi định giá thị trường</t>
         </is>
       </c>
-      <c r="C28" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="44" t="n">
+      <c r="C28" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="69" t="n">
         <v>350</v>
       </c>
-      <c r="G28" s="45">
+      <c r="G28" s="70">
         <f>SUM(C28:F28)</f>
         <v/>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="59">
         <f>ThamSo!$E$34</f>
         <v/>
       </c>
-      <c r="I28" s="45">
+      <c r="I28" s="70">
         <f>G28*H28</f>
         <v/>
       </c>
@@ -7192,7 +7215,7 @@
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.IV.2.5.b (raw dòng 1721); [[src-tt50-2026-nhnn#^pl1-b4]]</t>
+          <t>PL1.B.IV.2.5.b (raw dòng 1721); [[src-tt50-2026-nhnn#^pl1-b4-25]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7207,28 +7230,28 @@
           <t>Dòng tiền ra từ cam kết ngoại bảng</t>
         </is>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="67">
         <f>C30+C43+C47</f>
         <v/>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="67">
         <f>D30+D43+D47</f>
         <v/>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="67">
         <f>E30+E43+E47</f>
         <v/>
       </c>
-      <c r="F29" s="41">
+      <c r="F29" s="67">
         <f>F30+F43+F47</f>
         <v/>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="67">
         <f>G30+G43+G47</f>
         <v/>
       </c>
-      <c r="H29" s="42" t="n"/>
-      <c r="I29" s="41">
+      <c r="H29" s="68" t="n"/>
+      <c r="I29" s="67">
         <f>I30+I43+I47</f>
         <v/>
       </c>
@@ -7246,28 +7269,28 @@
           <t>Hạn mức cam kết chưa sử dụng</t>
         </is>
       </c>
-      <c r="C30" s="41">
+      <c r="C30" s="67">
         <f>C31+C32+C35+C38+C39+C42</f>
         <v/>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="67">
         <f>D31+D32+D35+D38+D39+D42</f>
         <v/>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="67">
         <f>E31+E32+E35+E38+E39+E42</f>
         <v/>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="67">
         <f>F31+F32+F35+F38+F39+F42</f>
         <v/>
       </c>
-      <c r="G30" s="41">
+      <c r="G30" s="67">
         <f>G31+G32+G35+G38+G39+G42</f>
         <v/>
       </c>
-      <c r="H30" s="42" t="n"/>
-      <c r="I30" s="41">
+      <c r="H30" s="68" t="n"/>
+      <c r="I30" s="67">
         <f>I31+I32+I35+I38+I39+I42</f>
         <v/>
       </c>
@@ -7289,27 +7312,27 @@
           <t>Đối với khách hàng bán lẻ và doanh nghiệp nhỏ và vừa đủ điều kiện</t>
         </is>
       </c>
-      <c r="C31" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="44" t="n">
+      <c r="C31" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="69" t="n">
         <v>6000</v>
       </c>
-      <c r="G31" s="45">
+      <c r="G31" s="70">
         <f>SUM(C31:F31)</f>
         <v/>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="59">
         <f>ThamSo!$E$35</f>
         <v/>
       </c>
-      <c r="I31" s="45">
+      <c r="I31" s="70">
         <f>G31*H31</f>
         <v/>
       </c>
@@ -7320,7 +7343,7 @@
       </c>
       <c r="K31" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.1.5.a (raw dòng 1748); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.1.5.a (raw dòng 1748); [[src-tt50-2026-nhnn#^pl1-b5]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7335,28 +7358,28 @@
           <t>Doanh nghiệp không phải tổ chức tài chính</t>
         </is>
       </c>
-      <c r="C32" s="41">
+      <c r="C32" s="67">
         <f>C33+C34</f>
         <v/>
       </c>
-      <c r="D32" s="41">
+      <c r="D32" s="67">
         <f>D33+D34</f>
         <v/>
       </c>
-      <c r="E32" s="41">
+      <c r="E32" s="67">
         <f>E33+E34</f>
         <v/>
       </c>
-      <c r="F32" s="41">
+      <c r="F32" s="67">
         <f>F33+F34</f>
         <v/>
       </c>
-      <c r="G32" s="41">
+      <c r="G32" s="67">
         <f>G33+G34</f>
         <v/>
       </c>
-      <c r="H32" s="42" t="n"/>
-      <c r="I32" s="41">
+      <c r="H32" s="68" t="n"/>
+      <c r="I32" s="67">
         <f>I33+I34</f>
         <v/>
       </c>
@@ -7378,27 +7401,27 @@
           <t xml:space="preserve">  – Hạn mức tín dụng</t>
         </is>
       </c>
-      <c r="C33" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="44" t="n">
+      <c r="C33" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="69" t="n">
         <v>12000</v>
       </c>
-      <c r="G33" s="45">
+      <c r="G33" s="70">
         <f>SUM(C33:F33)</f>
         <v/>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="59">
         <f>ThamSo!$E$36</f>
         <v/>
       </c>
-      <c r="I33" s="45">
+      <c r="I33" s="70">
         <f>G33*H33</f>
         <v/>
       </c>
@@ -7409,7 +7432,7 @@
       </c>
       <c r="K33" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.1.5.b (raw dòng 1749); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.1.5.b (raw dòng 1749); [[src-tt50-2026-nhnn#^pl1-b5]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7424,27 +7447,27 @@
           <t xml:space="preserve">  – Hạn mức thanh khoản</t>
         </is>
       </c>
-      <c r="C34" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="44" t="n">
+      <c r="C34" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="69" t="n">
         <v>800</v>
       </c>
-      <c r="G34" s="45">
+      <c r="G34" s="70">
         <f>SUM(C34:F34)</f>
         <v/>
       </c>
-      <c r="H34" s="24">
+      <c r="H34" s="59">
         <f>ThamSo!$E$37</f>
         <v/>
       </c>
-      <c r="I34" s="45">
+      <c r="I34" s="70">
         <f>G34*H34</f>
         <v/>
       </c>
@@ -7455,7 +7478,7 @@
       </c>
       <c r="K34" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.1.5.b (raw dòng 1749); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.1.5.b (raw dòng 1749); [[src-tt50-2026-nhnn#^pl1-b5]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7470,28 +7493,28 @@
           <t>Chính phủ, ngân hàng trung ương, tổ chức tài chính quốc tế và tổ chức công lập của Chính phủ</t>
         </is>
       </c>
-      <c r="C35" s="41">
+      <c r="C35" s="67">
         <f>C36+C37</f>
         <v/>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="67">
         <f>D36+D37</f>
         <v/>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="67">
         <f>E36+E37</f>
         <v/>
       </c>
-      <c r="F35" s="41">
+      <c r="F35" s="67">
         <f>F36+F37</f>
         <v/>
       </c>
-      <c r="G35" s="41">
+      <c r="G35" s="67">
         <f>G36+G37</f>
         <v/>
       </c>
-      <c r="H35" s="42" t="n"/>
-      <c r="I35" s="41">
+      <c r="H35" s="68" t="n"/>
+      <c r="I35" s="67">
         <f>I36+I37</f>
         <v/>
       </c>
@@ -7513,27 +7536,27 @@
           <t xml:space="preserve">  – Hạn mức tín dụng</t>
         </is>
       </c>
-      <c r="C36" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="45">
+      <c r="C36" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="70">
         <f>SUM(C36:F36)</f>
         <v/>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="59">
         <f>ThamSo!$E$38</f>
         <v/>
       </c>
-      <c r="I36" s="45">
+      <c r="I36" s="70">
         <f>G36*H36</f>
         <v/>
       </c>
@@ -7544,7 +7567,7 @@
       </c>
       <c r="K36" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.1.5.c (raw dòng 1750); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.1.5.c (raw dòng 1750); [[src-tt50-2026-nhnn#^pl1-b5]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7559,27 +7582,27 @@
           <t xml:space="preserve">  – Hạn mức thanh khoản</t>
         </is>
       </c>
-      <c r="C37" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="45">
+      <c r="C37" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="70">
         <f>SUM(C37:F37)</f>
         <v/>
       </c>
-      <c r="H37" s="24">
+      <c r="H37" s="59">
         <f>ThamSo!$E$39</f>
         <v/>
       </c>
-      <c r="I37" s="45">
+      <c r="I37" s="70">
         <f>G37*H37</f>
         <v/>
       </c>
@@ -7590,7 +7613,7 @@
       </c>
       <c r="K37" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.1.5.c (raw dòng 1750); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.1.5.c (raw dòng 1750); [[src-tt50-2026-nhnn#^pl1-b5]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7605,27 +7628,27 @@
           <t>Tổ chức tín dụng, chi nhánh ngân hàng nước ngoài</t>
         </is>
       </c>
-      <c r="C38" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="44" t="n">
+      <c r="C38" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="69" t="n">
         <v>500</v>
       </c>
-      <c r="G38" s="45">
+      <c r="G38" s="70">
         <f>SUM(C38:F38)</f>
         <v/>
       </c>
-      <c r="H38" s="24">
+      <c r="H38" s="59">
         <f>ThamSo!$E$40</f>
         <v/>
       </c>
-      <c r="I38" s="45">
+      <c r="I38" s="70">
         <f>G38*H38</f>
         <v/>
       </c>
@@ -7636,7 +7659,7 @@
       </c>
       <c r="K38" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.1.5.d (raw dòng 1751); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.1.5.d (raw dòng 1751); [[src-tt50-2026-nhnn#^pl1-b5]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7651,28 +7674,28 @@
           <t>Tổ chức tài chính khác (bao gồm công ty chứng khoán, bảo hiểm, công ty quản lý quỹ)</t>
         </is>
       </c>
-      <c r="C39" s="41">
+      <c r="C39" s="67">
         <f>C40+C41</f>
         <v/>
       </c>
-      <c r="D39" s="41">
+      <c r="D39" s="67">
         <f>D40+D41</f>
         <v/>
       </c>
-      <c r="E39" s="41">
+      <c r="E39" s="67">
         <f>E40+E41</f>
         <v/>
       </c>
-      <c r="F39" s="41">
+      <c r="F39" s="67">
         <f>F40+F41</f>
         <v/>
       </c>
-      <c r="G39" s="41">
+      <c r="G39" s="67">
         <f>G40+G41</f>
         <v/>
       </c>
-      <c r="H39" s="42" t="n"/>
-      <c r="I39" s="41">
+      <c r="H39" s="68" t="n"/>
+      <c r="I39" s="67">
         <f>I40+I41</f>
         <v/>
       </c>
@@ -7694,27 +7717,27 @@
           <t xml:space="preserve">  – Hạn mức tín dụng</t>
         </is>
       </c>
-      <c r="C40" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="45">
+      <c r="C40" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="70">
         <f>SUM(C40:F40)</f>
         <v/>
       </c>
-      <c r="H40" s="24">
+      <c r="H40" s="59">
         <f>ThamSo!$E$41</f>
         <v/>
       </c>
-      <c r="I40" s="45">
+      <c r="I40" s="70">
         <f>G40*H40</f>
         <v/>
       </c>
@@ -7725,7 +7748,7 @@
       </c>
       <c r="K40" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.1.5.đ (raw dòng 1752); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.1.5.đ (raw dòng 1752); [[src-tt50-2026-nhnn#^pl1-b5]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7740,27 +7763,27 @@
           <t xml:space="preserve">  – Hạn mức thanh khoản</t>
         </is>
       </c>
-      <c r="C41" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="45">
+      <c r="C41" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="70">
         <f>SUM(C41:F41)</f>
         <v/>
       </c>
-      <c r="H41" s="24">
+      <c r="H41" s="59">
         <f>ThamSo!$E$42</f>
         <v/>
       </c>
-      <c r="I41" s="45">
+      <c r="I41" s="70">
         <f>G41*H41</f>
         <v/>
       </c>
@@ -7771,7 +7794,7 @@
       </c>
       <c r="K41" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.1.5.đ (raw dòng 1752); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.1.5.đ (raw dòng 1752); [[src-tt50-2026-nhnn#^pl1-b5]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7786,27 +7809,27 @@
           <t>Khách hàng là đối tượng khác</t>
         </is>
       </c>
-      <c r="C42" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="45">
+      <c r="C42" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="70">
         <f>SUM(C42:F42)</f>
         <v/>
       </c>
-      <c r="H42" s="24">
+      <c r="H42" s="59">
         <f>ThamSo!$E$43</f>
         <v/>
       </c>
-      <c r="I42" s="45">
+      <c r="I42" s="70">
         <f>G42*H42</f>
         <v/>
       </c>
@@ -7817,7 +7840,7 @@
       </c>
       <c r="K42" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.1.5.e (raw dòng 1753); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.1.5.e (raw dòng 1753); [[src-tt50-2026-nhnn#^pl1-b5]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7832,28 +7855,28 @@
           <t>Dòng tiền từ nghĩa vụ giải ngân, thanh toán theo thỏa thuận</t>
         </is>
       </c>
-      <c r="C43" s="41">
+      <c r="C43" s="67">
         <f>C44+C45</f>
         <v/>
       </c>
-      <c r="D43" s="41">
+      <c r="D43" s="67">
         <f>D44+D45</f>
         <v/>
       </c>
-      <c r="E43" s="41">
+      <c r="E43" s="67">
         <f>E44+E45</f>
         <v/>
       </c>
-      <c r="F43" s="41">
+      <c r="F43" s="67">
         <f>F44+F45</f>
         <v/>
       </c>
-      <c r="G43" s="41">
+      <c r="G43" s="67">
         <f>G44+G45</f>
         <v/>
       </c>
-      <c r="H43" s="42" t="n"/>
-      <c r="I43" s="41">
+      <c r="H43" s="68" t="n"/>
+      <c r="I43" s="67">
         <f>I44+I45</f>
         <v/>
       </c>
@@ -7871,27 +7894,27 @@
           <t>Nghĩa vụ phải giải ngân, thanh toán trong vòng 30 ngày cho các tổ chức tài chính (bao gồm cả Ngân hàng Nhà nước)</t>
         </is>
       </c>
-      <c r="C44" s="44" t="n">
+      <c r="C44" s="69" t="n">
         <v>300</v>
       </c>
-      <c r="D44" s="44" t="n">
+      <c r="D44" s="69" t="n">
         <v>400</v>
       </c>
-      <c r="E44" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="45">
+      <c r="E44" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="70">
         <f>SUM(C44:F44)</f>
         <v/>
       </c>
-      <c r="H44" s="24">
+      <c r="H44" s="59">
         <f>ThamSo!$E$44</f>
         <v/>
       </c>
-      <c r="I44" s="45">
+      <c r="I44" s="70">
         <f>G44*H44</f>
         <v/>
       </c>
@@ -7902,7 +7925,7 @@
       </c>
       <c r="K44" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.2.1 (raw dòng 1759); [[src-tt50-2026-nhnn#^pl1-b5]]</t>
+          <t>PL1.B.V.2.1 (raw dòng 1759); [[src-tt50-2026-nhnn#^pl1-b5-2]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7917,27 +7940,27 @@
           <t>Nghĩa vụ phải giải ngân, thanh toán trong vòng 30 ngày cho các cá nhân và các tổ chức khác (không bao gồm tổ chức tài chính) — chỉ tính phần vượt 50% dòng vào từ cùng nhóm (dòng ngay dưới)</t>
         </is>
       </c>
-      <c r="C45" s="44" t="n">
+      <c r="C45" s="69" t="n">
         <v>500</v>
       </c>
-      <c r="D45" s="44" t="n">
+      <c r="D45" s="69" t="n">
         <v>1200</v>
       </c>
-      <c r="E45" s="44" t="n">
+      <c r="E45" s="69" t="n">
         <v>1500</v>
       </c>
-      <c r="F45" s="44" t="n">
+      <c r="F45" s="69" t="n">
         <v>2800</v>
       </c>
-      <c r="G45" s="45">
+      <c r="G45" s="70">
         <f>SUM(C45:F45)</f>
         <v/>
       </c>
-      <c r="H45" s="24">
+      <c r="H45" s="59">
         <f>ThamSo!$E$45</f>
         <v/>
       </c>
-      <c r="I45" s="45">
+      <c r="I45" s="70">
         <f>MAX(0,G45-ThamSo!$E$46*G46)*H45</f>
         <v/>
       </c>
@@ -7948,7 +7971,7 @@
       </c>
       <c r="K45" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.2.2 (raw dòng 1761); chưa có claim trong source note</t>
+          <t>PL1.B.V.2.2 (raw dòng 1761); [[src-tt50-2026-nhnn#^pl1-b5-2]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -7963,24 +7986,24 @@
           <t xml:space="preserve">  Ghi nhớ (không cộng vào tổng): dòng tiền vào trong 30 ngày từ cá nhân và tổ chức khác (không phải tổ chức tài chính)</t>
         </is>
       </c>
-      <c r="C46" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="44" t="n">
+      <c r="C46" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="69" t="n">
         <v>7000</v>
       </c>
-      <c r="G46" s="52">
+      <c r="G46" s="75">
         <f>SUM(C46:F46)</f>
         <v/>
       </c>
-      <c r="H46" s="53" t="n"/>
-      <c r="I46" s="52" t="n"/>
+      <c r="H46" s="76" t="n"/>
+      <c r="I46" s="75" t="n"/>
       <c r="J46" s="18" t="inlineStr">
         <is>
           <t>Dùng để tính ngưỡng 50% của mục 5.2.2</t>
@@ -8003,28 +8026,28 @@
           <t>Dòng tiền ra từ các nghĩa vụ nợ tiềm ẩn khác</t>
         </is>
       </c>
-      <c r="C47" s="41">
+      <c r="C47" s="67">
         <f>C48+C52+C53+C54</f>
         <v/>
       </c>
-      <c r="D47" s="41">
+      <c r="D47" s="67">
         <f>D48+D52+D53+D54</f>
         <v/>
       </c>
-      <c r="E47" s="41">
+      <c r="E47" s="67">
         <f>E48+E52+E53+E54</f>
         <v/>
       </c>
-      <c r="F47" s="41">
+      <c r="F47" s="67">
         <f>F48+F52+F53+F54</f>
         <v/>
       </c>
-      <c r="G47" s="41">
+      <c r="G47" s="67">
         <f>G48+G52+G53+G54</f>
         <v/>
       </c>
-      <c r="H47" s="42" t="n"/>
-      <c r="I47" s="41">
+      <c r="H47" s="68" t="n"/>
+      <c r="I47" s="67">
         <f>I48+I52+I53+I54</f>
         <v/>
       </c>
@@ -8042,28 +8065,28 @@
           <t>Các nghĩa vụ nợ tiềm ẩn theo hợp đồng</t>
         </is>
       </c>
-      <c r="C48" s="41">
+      <c r="C48" s="67">
         <f>C49+C50+C51</f>
         <v/>
       </c>
-      <c r="D48" s="41">
+      <c r="D48" s="67">
         <f>D49+D50+D51</f>
         <v/>
       </c>
-      <c r="E48" s="41">
+      <c r="E48" s="67">
         <f>E49+E50+E51</f>
         <v/>
       </c>
-      <c r="F48" s="41">
+      <c r="F48" s="67">
         <f>F49+F50+F51</f>
         <v/>
       </c>
-      <c r="G48" s="41">
+      <c r="G48" s="67">
         <f>G49+G50+G51</f>
         <v/>
       </c>
-      <c r="H48" s="42" t="n"/>
-      <c r="I48" s="41">
+      <c r="H48" s="68" t="n"/>
+      <c r="I48" s="67">
         <f>I49+I50+I51</f>
         <v/>
       </c>
@@ -8081,27 +8104,27 @@
           <t xml:space="preserve">  – Hạn mức huỷ ngang vô điều kiện; cam kết cung cấp cam kết ngoại bảng khác [a(i), a(iv)]</t>
         </is>
       </c>
-      <c r="C49" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="44" t="n">
+      <c r="C49" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="69" t="n">
         <v>3000</v>
       </c>
-      <c r="G49" s="45">
+      <c r="G49" s="70">
         <f>SUM(C49:F49)</f>
         <v/>
       </c>
-      <c r="H49" s="24">
+      <c r="H49" s="59">
         <f>ThamSo!$E$47</f>
         <v/>
       </c>
-      <c r="I49" s="45">
+      <c r="I49" s="70">
         <f>G49*H49</f>
         <v/>
       </c>
@@ -8112,7 +8135,7 @@
       </c>
       <c r="K49" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.3.2.a (raw dòng 1785); [[src-tt50-2026-nhnn#^pl1-b5-3]]</t>
+          <t>PL1.B.V.3.2.a (raw dòng 1785); [[src-tt50-2026-nhnn#^pl1-b5-31]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -8127,27 +8150,27 @@
           <t xml:space="preserve">  – Công cụ tài trợ thương mại [a(ii)]</t>
         </is>
       </c>
-      <c r="C50" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="44" t="n">
+      <c r="C50" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="69" t="n">
         <v>4000</v>
       </c>
-      <c r="G50" s="45">
+      <c r="G50" s="70">
         <f>SUM(C50:F50)</f>
         <v/>
       </c>
-      <c r="H50" s="24">
+      <c r="H50" s="59">
         <f>ThamSo!$E$48</f>
         <v/>
       </c>
-      <c r="I50" s="45">
+      <c r="I50" s="70">
         <f>G50*H50</f>
         <v/>
       </c>
@@ -8158,7 +8181,7 @@
       </c>
       <c r="K50" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.3.2.b (raw dòng 1787); [[src-tt50-2026-nhnn#^pl1-b5-3]]</t>
+          <t>PL1.B.V.3.2.b (raw dòng 1787); [[src-tt50-2026-nhnn#^pl1-b5-31]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -8173,27 +8196,27 @@
           <t xml:space="preserve">  – Bảo lãnh ngân hàng, dự thầu, thực hiện hợp đồng; autocallable [a(iii), a(v)]</t>
         </is>
       </c>
-      <c r="C51" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="44" t="n">
+      <c r="C51" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="69" t="n">
         <v>15000</v>
       </c>
-      <c r="G51" s="45">
+      <c r="G51" s="70">
         <f>SUM(C51:F51)</f>
         <v/>
       </c>
-      <c r="H51" s="24">
+      <c r="H51" s="59">
         <f>ThamSo!$E$49</f>
         <v/>
       </c>
-      <c r="I51" s="45">
+      <c r="I51" s="70">
         <f>G51*H51</f>
         <v/>
       </c>
@@ -8204,7 +8227,7 @@
       </c>
       <c r="K51" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.3.2.c (raw dòng 1789); [[src-tt50-2026-nhnn#^pl1-b5-3]]</t>
+          <t>PL1.B.V.3.2.c (raw dòng 1789); [[src-tt50-2026-nhnn#^pl1-b5-31]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -8219,27 +8242,27 @@
           <t>Các nghĩa vụ tiềm ẩn phi hợp đồng</t>
         </is>
       </c>
-      <c r="C52" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="45">
+      <c r="C52" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="70">
         <f>SUM(C52:F52)</f>
         <v/>
       </c>
-      <c r="H52" s="24">
+      <c r="H52" s="59">
         <f>ThamSo!$E$50</f>
         <v/>
       </c>
-      <c r="I52" s="45">
+      <c r="I52" s="70">
         <f>G52*H52</f>
         <v/>
       </c>
@@ -8250,7 +8273,7 @@
       </c>
       <c r="K52" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.3.2.d (raw dòng 1791); [[src-tt50-2026-nhnn#^pl1-b5-3]]</t>
+          <t>PL1.B.V.3.2.d (raw dòng 1791); [[src-tt50-2026-nhnn#^pl1-b5-31]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -8265,27 +8288,27 @@
           <t>Cam kết ngoại bảng khác</t>
         </is>
       </c>
-      <c r="C53" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="45">
+      <c r="C53" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="70">
         <f>SUM(C53:F53)</f>
         <v/>
       </c>
-      <c r="H53" s="24">
+      <c r="H53" s="59">
         <f>ThamSo!$E$51</f>
         <v/>
       </c>
-      <c r="I53" s="45">
+      <c r="I53" s="70">
         <f>G53*H53</f>
         <v/>
       </c>
@@ -8296,7 +8319,7 @@
       </c>
       <c r="K53" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.3.2.d (raw dòng 1791); [[src-tt50-2026-nhnn#^pl1-b5-3]]</t>
+          <t>PL1.B.V.3.2.d (raw dòng 1791); [[src-tt50-2026-nhnn#^pl1-b5-31]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -8311,27 +8334,27 @@
           <t>Nghĩa vụ nợ tiềm ẩn phát sinh sự kiện cụ thể kích hoạt hợp đồng theo thỏa thuận</t>
         </is>
       </c>
-      <c r="C54" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="45">
+      <c r="C54" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="70">
         <f>SUM(C54:F54)</f>
         <v/>
       </c>
-      <c r="H54" s="24">
+      <c r="H54" s="59">
         <f>ThamSo!$E$52</f>
         <v/>
       </c>
-      <c r="I54" s="45">
+      <c r="I54" s="70">
         <f>G54*H54</f>
         <v/>
       </c>
@@ -8342,7 +8365,7 @@
       </c>
       <c r="K54" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.V.3.3 (raw dòng 1793); chưa có claim trong source note</t>
+          <t>PL1.B.V.3.3 (raw dòng 1793); [[src-tt50-2026-nhnn#^pl1-b5-31]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -8357,27 +8380,27 @@
           <t>Dòng tiền ra ròng từ các hợp đồng phái sinh</t>
         </is>
       </c>
-      <c r="C55" s="44" t="n">
+      <c r="C55" s="69" t="n">
         <v>50</v>
       </c>
-      <c r="D55" s="44" t="n">
+      <c r="D55" s="69" t="n">
         <v>120</v>
       </c>
-      <c r="E55" s="44" t="n">
+      <c r="E55" s="69" t="n">
         <v>80</v>
       </c>
-      <c r="F55" s="44" t="n">
+      <c r="F55" s="69" t="n">
         <v>200</v>
       </c>
-      <c r="G55" s="45">
+      <c r="G55" s="70">
         <f>SUM(C55:F55)</f>
         <v/>
       </c>
-      <c r="H55" s="24">
+      <c r="H55" s="59">
         <f>ThamSo!$E$53</f>
         <v/>
       </c>
-      <c r="I55" s="45">
+      <c r="I55" s="70">
         <f>G55*H55</f>
         <v/>
       </c>
@@ -8388,7 +8411,7 @@
       </c>
       <c r="K55" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.IV.1.2 (raw dòng 1663); [[src-tt50-2026-nhnn#^pl1-b4]]</t>
+          <t>PL1.B.IV.1.2 (raw dòng 1663); [[src-tt50-2026-nhnn#^pl1-b4-1]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -8403,27 +8426,27 @@
           <t>Dòng tiền ra theo thỏa thuận khác</t>
         </is>
       </c>
-      <c r="C56" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="45">
+      <c r="C56" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="70">
         <f>SUM(C56:F56)</f>
         <v/>
       </c>
-      <c r="H56" s="24">
+      <c r="H56" s="59">
         <f>ThamSo!$E$54</f>
         <v/>
       </c>
-      <c r="I56" s="45">
+      <c r="I56" s="70">
         <f>G56*H56</f>
         <v/>
       </c>
@@ -8434,7 +8457,7 @@
       </c>
       <c r="K56" s="18" t="inlineStr">
         <is>
-          <t>PL1.B.VI.2 (raw dòng 1799); chưa có claim trong source note</t>
+          <t>PL1.B.VI.2 (raw dòng 1799); [[src-tt50-2026-nhnn#^pl1-b6]] [[src-tt50-2026-nhnn#^pl1-b7]]</t>
         </is>
       </c>
     </row>
@@ -8444,29 +8467,29 @@
           <t>Tổng dòng tiền ra</t>
         </is>
       </c>
-      <c r="B57" s="54" t="n"/>
-      <c r="C57" s="49">
+      <c r="B57" s="73" t="n"/>
+      <c r="C57" s="74">
         <f>C6+C9+C16+C23+C29+C55+C56</f>
         <v/>
       </c>
-      <c r="D57" s="49">
+      <c r="D57" s="74">
         <f>D6+D9+D16+D23+D29+D55+D56</f>
         <v/>
       </c>
-      <c r="E57" s="49">
+      <c r="E57" s="74">
         <f>E6+E9+E16+E23+E29+E55+E56</f>
         <v/>
       </c>
-      <c r="F57" s="49">
+      <c r="F57" s="74">
         <f>F6+F9+F16+F23+F29+F55+F56</f>
         <v/>
       </c>
-      <c r="G57" s="49">
+      <c r="G57" s="74">
         <f>G6+G9+G16+G23+G29+G55+G56</f>
         <v/>
       </c>
       <c r="H57" s="48" t="n"/>
-      <c r="I57" s="49">
+      <c r="I57" s="74">
         <f>I6+I9+I16+I23+I29+I55+I56</f>
         <v/>
       </c>
@@ -8528,16 +8551,6 @@
           <t>Đơn vị: tỷ đồng. Ô nền vàng chữ xanh = nhập liệu. Số đang có là SỐ LIỆU MINH HOẠ, thay bằng số liệu thật. Cột (1)–(4): số dư đủ điều kiện phân theo thời gian đến hạn theo hợp đồng/dự kiến.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n"/>
@@ -8661,28 +8674,28 @@
           <t>Khoản cấp tín dụng có bảo đảm bằng tài sản tài chính hoặc giao dịch mua lại đảo ngược (reverse repo)</t>
         </is>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="67">
         <f>C7+C8+C9+C12+C13</f>
         <v/>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="67">
         <f>D7+D8+D9+D12+D13</f>
         <v/>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="67">
         <f>E7+E8+E9+E12+E13</f>
         <v/>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="67">
         <f>F7+F8+F9+F12+F13</f>
         <v/>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="67">
         <f>G7+G8+G9+G12+G13</f>
         <v/>
       </c>
-      <c r="H6" s="42" t="n"/>
-      <c r="I6" s="41">
+      <c r="H6" s="68" t="n"/>
+      <c r="I6" s="67">
         <f>I7+I8+I9+I12+I13</f>
         <v/>
       </c>
@@ -8700,27 +8713,27 @@
           <t>Tài sản cấp 1</t>
         </is>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="69" t="n">
         <v>1000</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="69" t="n">
         <v>500</v>
       </c>
-      <c r="E7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="45">
+      <c r="E7" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="70">
         <f>SUM(C7:F7)</f>
         <v/>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="59">
         <f>ThamSo!$E$55</f>
         <v/>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="70">
         <f>G7*H7</f>
         <v/>
       </c>
@@ -8731,7 +8744,7 @@
       </c>
       <c r="K7" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.II.4.a (raw dòng 1900); [[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>PL1.C.II.4.a (raw dòng 1900); [[src-tt50-2026-nhnn#^pl1-c2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -8746,27 +8759,27 @@
           <t>Tài sản cấp 2A</t>
         </is>
       </c>
-      <c r="C8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="44" t="n">
+      <c r="C8" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="69" t="n">
         <v>200</v>
       </c>
-      <c r="E8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="45">
+      <c r="E8" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="70">
         <f>SUM(C8:F8)</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="59">
         <f>ThamSo!$E$56</f>
         <v/>
       </c>
-      <c r="I8" s="45">
+      <c r="I8" s="70">
         <f>G8*H8</f>
         <v/>
       </c>
@@ -8777,7 +8790,7 @@
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.II.4.b (raw dòng 1901); [[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>PL1.C.II.4.b (raw dòng 1901); [[src-tt50-2026-nhnn#^pl1-c2-2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -8792,28 +8805,28 @@
           <t>Tài sản cấp 2B</t>
         </is>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="67">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="67">
         <f>D10+D11</f>
         <v/>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="67">
         <f>E10+E11</f>
         <v/>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="67">
         <f>F10+F11</f>
         <v/>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="67">
         <f>G10+G11</f>
         <v/>
       </c>
-      <c r="H9" s="42" t="n"/>
-      <c r="I9" s="41">
+      <c r="H9" s="68" t="n"/>
+      <c r="I9" s="67">
         <f>I10+I11</f>
         <v/>
       </c>
@@ -8831,27 +8844,27 @@
           <t>RMBS đủ điều kiện</t>
         </is>
       </c>
-      <c r="C10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="45">
+      <c r="C10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="70">
         <f>SUM(C10:F10)</f>
         <v/>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="59">
         <f>ThamSo!$E$57</f>
         <v/>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="70">
         <f>G10*H10</f>
         <v/>
       </c>
@@ -8862,7 +8875,7 @@
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.II.4.c (raw dòng 1902); [[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>PL1.C.II.4.c (raw dòng 1902); [[src-tt50-2026-nhnn#^pl1-c2-2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -8877,27 +8890,27 @@
           <t>Tài sản cấp 2B khác</t>
         </is>
       </c>
-      <c r="C11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="45">
+      <c r="C11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="70">
         <f>SUM(C11:F11)</f>
         <v/>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="59">
         <f>ThamSo!$E$58</f>
         <v/>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="70">
         <f>G11*H11</f>
         <v/>
       </c>
@@ -8908,7 +8921,7 @@
       </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.II.4.d (raw dòng 1903); [[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>PL1.C.II.4.d (raw dòng 1903); [[src-tt50-2026-nhnn#^pl1-c2-2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -8923,27 +8936,27 @@
           <t>Khoản cho vay ký quỹ</t>
         </is>
       </c>
-      <c r="C12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="45">
+      <c r="C12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="70">
         <f>SUM(C12:F12)</f>
         <v/>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="59">
         <f>ThamSo!$E$59</f>
         <v/>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="70">
         <f>G12*H12</f>
         <v/>
       </c>
@@ -8954,7 +8967,7 @@
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.II.4.đ (raw dòng 1904); [[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>PL1.C.II.4.đ (raw dòng 1904); [[src-tt50-2026-nhnn#^pl1-c2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -8969,27 +8982,27 @@
           <t>Các tài sản tài chính khác</t>
         </is>
       </c>
-      <c r="C13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="44" t="n">
+      <c r="C13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="69" t="n">
         <v>300</v>
       </c>
-      <c r="F13" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="45">
+      <c r="F13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="70">
         <f>SUM(C13:F13)</f>
         <v/>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="59">
         <f>ThamSo!$E$60</f>
         <v/>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="70">
         <f>G13*H13</f>
         <v/>
       </c>
@@ -9000,7 +9013,7 @@
       </c>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.II.4.e (raw dòng 1905); [[src-tt50-2026-nhnn#^pl1-c2]]</t>
+          <t>PL1.C.II.4.e (raw dòng 1905); [[src-tt50-2026-nhnn#^pl1-c2-2]] [[src-tt50-2026-nhnn#^pl1-c2-4]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9015,27 +9028,27 @@
           <t>Hạn mức tín dụng hoặc thanh khoản được cung cấp cho ngân hàng báo cáo</t>
         </is>
       </c>
-      <c r="C14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="45">
+      <c r="C14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="70">
         <f>SUM(C14:F14)</f>
         <v/>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="59">
         <f>ThamSo!$E$61</f>
         <v/>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="70">
         <f>G14*H14</f>
         <v/>
       </c>
@@ -9046,7 +9059,7 @@
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.III (raw dòng 1911); [[src-tt50-2026-nhnn#^pl1-c1]]</t>
+          <t>PL1.C.III (raw dòng 1911); [[src-tt50-2026-nhnn#^pl1-c3]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9061,28 +9074,28 @@
           <t>Tiền gửi hoạt động</t>
         </is>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="67">
         <f>C16+C17</f>
         <v/>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="67">
         <f>D16+D17</f>
         <v/>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="67">
         <f>E16+E17</f>
         <v/>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="67">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="67">
         <f>G16+G17</f>
         <v/>
       </c>
-      <c r="H15" s="42" t="n"/>
-      <c r="I15" s="41">
+      <c r="H15" s="68" t="n"/>
+      <c r="I15" s="67">
         <f>I16+I17</f>
         <v/>
       </c>
@@ -9104,27 +9117,27 @@
           <t>Tiền gửi hoạt động tại các tổ chức tài chính khác</t>
         </is>
       </c>
-      <c r="C16" s="44" t="n">
+      <c r="C16" s="69" t="n">
         <v>800</v>
       </c>
-      <c r="D16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="45">
+      <c r="D16" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="70">
         <f>SUM(C16:F16)</f>
         <v/>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="59">
         <f>ThamSo!$E$62</f>
         <v/>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="70">
         <f>G16*H16</f>
         <v/>
       </c>
@@ -9135,7 +9148,7 @@
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.8.a (raw dòng 1949); [[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>PL1.C.IV.8.a (raw dòng 1949); [[src-tt50-2026-nhnn#^pl1-c4-8a]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9150,27 +9163,27 @@
           <t>Phần tiền gửi dư thừa đủ điều kiện</t>
         </is>
       </c>
-      <c r="C17" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="45">
+      <c r="C17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="70">
         <f>SUM(C17:F17)</f>
         <v/>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="59">
         <f>ThamSo!$E$63</f>
         <v/>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="70">
         <f>G17*H17</f>
         <v/>
       </c>
@@ -9181,7 +9194,7 @@
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.8.b (raw dòng 1951); chưa có claim trong source note</t>
+          <t>PL1.C.IV.8.b (raw dòng 1951); [[src-tt50-2026-nhnn#^pl1-c4-8b]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9196,28 +9209,28 @@
           <t>Tiền gửi phát sinh từ hoạt động ngân hàng đại lý</t>
         </is>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="67">
         <f>C19+C20</f>
         <v/>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="67">
         <f>D19+D20</f>
         <v/>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="67">
         <f>E19+E20</f>
         <v/>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="67">
         <f>F19+F20</f>
         <v/>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="67">
         <f>G19+G20</f>
         <v/>
       </c>
-      <c r="H18" s="42" t="n"/>
-      <c r="I18" s="41">
+      <c r="H18" s="68" t="n"/>
+      <c r="I18" s="67">
         <f>I19+I20</f>
         <v/>
       </c>
@@ -9235,27 +9248,27 @@
           <t>Tiền gửi từ hoạt động ngân hàng đại lý</t>
         </is>
       </c>
-      <c r="C19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="45">
+      <c r="C19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="70">
         <f>SUM(C19:F19)</f>
         <v/>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="59">
         <f>ThamSo!$E$64</f>
         <v/>
       </c>
-      <c r="I19" s="45">
+      <c r="I19" s="70">
         <f>G19*H19</f>
         <v/>
       </c>
@@ -9266,7 +9279,7 @@
       </c>
       <c r="K19" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.9 (raw dòng 1953); chưa có claim trong source note</t>
+          <t>PL1.C.IV.9 (raw dòng 1953); [[src-tt50-2026-nhnn#^pl1-c4-9]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9281,27 +9294,27 @@
           <t>Phần tiền gửi dư thừa đủ điều kiện</t>
         </is>
       </c>
-      <c r="C20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="45">
+      <c r="C20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="70">
         <f>SUM(C20:F20)</f>
         <v/>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="59">
         <f>ThamSo!$E$65</f>
         <v/>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="70">
         <f>G20*H20</f>
         <v/>
       </c>
@@ -9312,7 +9325,7 @@
       </c>
       <c r="K20" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.9 (raw dòng 1953); chưa có claim trong source note</t>
+          <t>PL1.C.IV.9 (raw dòng 1953); [[src-tt50-2026-nhnn#^pl1-c4-9]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9327,28 +9340,28 @@
           <t>Các dòng tiền vào theo đối tác</t>
         </is>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="67">
         <f>C22+C23+C27</f>
         <v/>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="67">
         <f>D22+D23+D27</f>
         <v/>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="67">
         <f>E22+E23+E27</f>
         <v/>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="67">
         <f>F22+F23+F27</f>
         <v/>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="67">
         <f>G22+G23+G27</f>
         <v/>
       </c>
-      <c r="H21" s="42" t="n"/>
-      <c r="I21" s="41">
+      <c r="H21" s="68" t="n"/>
+      <c r="I21" s="67">
         <f>I22+I23+I27</f>
         <v/>
       </c>
@@ -9370,27 +9383,27 @@
           <t>Khoản tiền phải thu từ khách hàng bán lẻ và doanh nghiệp nhỏ và vừa đủ điều kiện</t>
         </is>
       </c>
-      <c r="C22" s="44" t="n">
+      <c r="C22" s="69" t="n">
         <v>300</v>
       </c>
-      <c r="D22" s="44" t="n">
+      <c r="D22" s="69" t="n">
         <v>700</v>
       </c>
-      <c r="E22" s="44" t="n">
+      <c r="E22" s="69" t="n">
         <v>800</v>
       </c>
-      <c r="F22" s="44" t="n">
+      <c r="F22" s="69" t="n">
         <v>1800</v>
       </c>
-      <c r="G22" s="45">
+      <c r="G22" s="70">
         <f>SUM(C22:F22)</f>
         <v/>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="59">
         <f>ThamSo!$E$66</f>
         <v/>
       </c>
-      <c r="I22" s="45">
+      <c r="I22" s="70">
         <f>G22*H22</f>
         <v/>
       </c>
@@ -9401,7 +9414,7 @@
       </c>
       <c r="K22" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.5 (raw dòng 1925); [[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>PL1.C.IV.5 (raw dòng 1925); [[src-tt50-2026-nhnn#^pl1-c4-5]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9416,28 +9429,28 @@
           <t>Khoản tiền phải thu từ doanh nghiệp, Chính phủ, tổ chức tài chính quốc tế, tổ chức công lập của Chính phủ</t>
         </is>
       </c>
-      <c r="C23" s="41">
+      <c r="C23" s="67">
         <f>C24+C25+C26</f>
         <v/>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="67">
         <f>D24+D25+D26</f>
         <v/>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="67">
         <f>E24+E25+E26</f>
         <v/>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="67">
         <f>F24+F25+F26</f>
         <v/>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="67">
         <f>G24+G25+G26</f>
         <v/>
       </c>
-      <c r="H23" s="42" t="n"/>
-      <c r="I23" s="41">
+      <c r="H23" s="68" t="n"/>
+      <c r="I23" s="67">
         <f>I24+I25+I26</f>
         <v/>
       </c>
@@ -9455,27 +9468,27 @@
           <t>Doanh nghiệp không phải tổ chức tài chính</t>
         </is>
       </c>
-      <c r="C24" s="44" t="n">
+      <c r="C24" s="69" t="n">
         <v>400</v>
       </c>
-      <c r="D24" s="44" t="n">
+      <c r="D24" s="69" t="n">
         <v>900</v>
       </c>
-      <c r="E24" s="44" t="n">
+      <c r="E24" s="69" t="n">
         <v>1100</v>
       </c>
-      <c r="F24" s="44" t="n">
+      <c r="F24" s="69" t="n">
         <v>2400</v>
       </c>
-      <c r="G24" s="45">
+      <c r="G24" s="70">
         <f>SUM(C24:F24)</f>
         <v/>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="59">
         <f>ThamSo!$E$67</f>
         <v/>
       </c>
-      <c r="I24" s="45">
+      <c r="I24" s="70">
         <f>G24*H24</f>
         <v/>
       </c>
@@ -9486,7 +9499,7 @@
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.6.b(i) (raw dòng 1933); [[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>PL1.C.IV.6.b(i) (raw dòng 1933); [[src-tt50-2026-nhnn#^pl1-c4-6b]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9501,27 +9514,27 @@
           <t>Chính phủ; Kho bạc Nhà nước, Ủy ban nhân dân tỉnh, thành phố trực thuộc Trung ương; Bảo hiểm tiền gửi Việt Nam</t>
         </is>
       </c>
-      <c r="C25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="45">
+      <c r="C25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="70">
         <f>SUM(C25:F25)</f>
         <v/>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="59">
         <f>ThamSo!$E$68</f>
         <v/>
       </c>
-      <c r="I25" s="45">
+      <c r="I25" s="70">
         <f>G25*H25</f>
         <v/>
       </c>
@@ -9532,7 +9545,7 @@
       </c>
       <c r="K25" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.6.b(ii) (raw dòng 1935); [[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>PL1.C.IV.6.b(ii) (raw dòng 1935); [[src-tt50-2026-nhnn#^pl1-c4-6b]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9547,27 +9560,27 @@
           <t>Các tổ chức khác</t>
         </is>
       </c>
-      <c r="C26" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="45">
+      <c r="C26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="70">
         <f>SUM(C26:F26)</f>
         <v/>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="59">
         <f>ThamSo!$E$69</f>
         <v/>
       </c>
-      <c r="I26" s="45">
+      <c r="I26" s="70">
         <f>G26*H26</f>
         <v/>
       </c>
@@ -9578,7 +9591,7 @@
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.6.b(iii)–(v) (raw dòng 1937); [[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>PL1.C.IV.6.b(iii)–(v) (raw dòng 1937); [[src-tt50-2026-nhnn#^pl1-c4-6b]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9593,27 +9606,27 @@
           <t>Khoản tiền phải thu từ tổ chức tài chính và Ngân hàng Nhà nước</t>
         </is>
       </c>
-      <c r="C27" s="44" t="n">
+      <c r="C27" s="69" t="n">
         <v>800</v>
       </c>
-      <c r="D27" s="44" t="n">
+      <c r="D27" s="69" t="n">
         <v>600</v>
       </c>
-      <c r="E27" s="44" t="n">
+      <c r="E27" s="69" t="n">
         <v>500</v>
       </c>
-      <c r="F27" s="44" t="n">
+      <c r="F27" s="69" t="n">
         <v>700</v>
       </c>
-      <c r="G27" s="45">
+      <c r="G27" s="70">
         <f>SUM(C27:F27)</f>
         <v/>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="59">
         <f>ThamSo!$E$70</f>
         <v/>
       </c>
-      <c r="I27" s="45">
+      <c r="I27" s="70">
         <f>G27*H27</f>
         <v/>
       </c>
@@ -9624,7 +9637,7 @@
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.6.a (raw dòng 1929); [[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>PL1.C.IV.6.a (raw dòng 1929); [[src-tt50-2026-nhnn#^pl1-c4-6a]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9639,27 +9652,27 @@
           <t>Dòng tiền vào ròng từ công cụ phái sinh</t>
         </is>
       </c>
-      <c r="C28" s="44" t="n">
+      <c r="C28" s="69" t="n">
         <v>40</v>
       </c>
-      <c r="D28" s="44" t="n">
+      <c r="D28" s="69" t="n">
         <v>90</v>
       </c>
-      <c r="E28" s="44" t="n">
+      <c r="E28" s="69" t="n">
         <v>60</v>
       </c>
-      <c r="F28" s="44" t="n">
+      <c r="F28" s="69" t="n">
         <v>150</v>
       </c>
-      <c r="G28" s="45">
+      <c r="G28" s="70">
         <f>SUM(C28:F28)</f>
         <v/>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="59">
         <f>ThamSo!$E$71</f>
         <v/>
       </c>
-      <c r="I28" s="45">
+      <c r="I28" s="70">
         <f>G28*H28</f>
         <v/>
       </c>
@@ -9670,7 +9683,7 @@
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.V.1 (raw dòng 1957); chưa có claim trong source note</t>
+          <t>PL1.C.V.1 (raw dòng 1957); [[src-tt50-2026-nhnn#^pl1-c5-1]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9685,27 +9698,27 @@
           <t>Dòng tiền vào từ chứng khoán đáo hạn trong vòng 30 ngày nhưng chứng khoán không thuộc danh mục HQLA đủ tiêu chuẩn</t>
         </is>
       </c>
-      <c r="C29" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="44" t="n">
+      <c r="C29" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="69" t="n">
         <v>300</v>
       </c>
-      <c r="E29" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="44" t="n">
+      <c r="E29" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="69" t="n">
         <v>500</v>
       </c>
-      <c r="G29" s="45">
+      <c r="G29" s="70">
         <f>SUM(C29:F29)</f>
         <v/>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="59">
         <f>ThamSo!$E$72</f>
         <v/>
       </c>
-      <c r="I29" s="45">
+      <c r="I29" s="70">
         <f>G29*H29</f>
         <v/>
       </c>
@@ -9716,7 +9729,7 @@
       </c>
       <c r="K29" s="18" t="inlineStr">
         <is>
-          <t>PL1.C.IV.7 (raw dòng 1943); [[src-tt50-2026-nhnn#^pl1-c4]]</t>
+          <t>PL1.C.IV.7 (raw dòng 1943); [[src-tt50-2026-nhnn#^pl1-c4-7]] [[src-tt50-2026-nhnn#^pl1-c7]]</t>
         </is>
       </c>
     </row>
@@ -9726,29 +9739,29 @@
           <t>Tổng dòng tiền vào</t>
         </is>
       </c>
-      <c r="B30" s="54" t="n"/>
-      <c r="C30" s="49">
+      <c r="B30" s="73" t="n"/>
+      <c r="C30" s="74">
         <f>C6+C14+C15+C18+C21+C28+C29</f>
         <v/>
       </c>
-      <c r="D30" s="49">
+      <c r="D30" s="74">
         <f>D6+D14+D15+D18+D21+D28+D29</f>
         <v/>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="74">
         <f>E6+E14+E15+E18+E21+E28+E29</f>
         <v/>
       </c>
-      <c r="F30" s="49">
+      <c r="F30" s="74">
         <f>F6+F14+F15+F18+F21+F28+F29</f>
         <v/>
       </c>
-      <c r="G30" s="49">
+      <c r="G30" s="74">
         <f>G6+G14+G15+G18+G21+G28+G29</f>
         <v/>
       </c>
       <c r="H30" s="48" t="n"/>
-      <c r="I30" s="49">
+      <c r="I30" s="74">
         <f>I6+I14+I15+I18+I21+I28+I29</f>
         <v/>
       </c>
